--- a/tools/importer/reports/import-app-entry.report.xlsx
+++ b/tools/importer/reports/import-app-entry.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="906">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,9 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>fragment</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -37,6 +40,318 @@
     <t>url</t>
   </si>
   <si>
+    <t>at/de/footer.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>footer</t>
+  </si>
+  <si>
+    <t>at/de/footer</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>nav</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:55:06.747Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/at/de/homepage#footer</t>
+  </si>
+  <si>
+    <t>at/de/homepage.report.json</t>
+  </si>
+  <si>
+    <t>["flight-search","hero-card-overlay","fare-teaser","carousel-cards","destination-finder","cards-icon","columns-logos","accordion-columns"]</t>
+  </si>
+  <si>
+    <t>at/de/homepage</t>
+  </si>
+  <si>
+    <t>homepage</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:28:43.065Z</t>
+  </si>
+  <si>
+    <t>Jetzt Flug buchen – mit Lufthansa zu über 200 Zielen reisen | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/at/de/homepage</t>
+  </si>
+  <si>
+    <t>at/de/nav.report.json</t>
+  </si>
+  <si>
+    <t>at/de/nav</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:55:02.759Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/at/de/homepage#nav</t>
+  </si>
+  <si>
+    <t>de/de/doctor-on-board-news.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-columns","carousel-cards"]</t>
+  </si>
+  <si>
+    <t>de/de/doctor-on-board-news</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:06.345Z</t>
+  </si>
+  <si>
+    <t>Doctor on Board – Gut zu wissen | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/doctor-on-board-news</t>
+  </si>
+  <si>
+    <t>de/de/doctor-on-board.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>de/de/doctor-on-board</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:01.082Z</t>
+  </si>
+  <si>
+    <t>Doctor on Board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/doctor-on-board</t>
+  </si>
+  <si>
+    <t>de/de/footer.report.json</t>
+  </si>
+  <si>
+    <t>de/de/footer</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:54:56.409Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/homepage#footer</t>
+  </si>
+  <si>
+    <t>de/de/homepage.report.json</t>
+  </si>
+  <si>
+    <t>de/de/homepage</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:28:39.550Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/homepage</t>
+  </si>
+  <si>
+    <t>de/de/kinder-an-bord.report.json</t>
+  </si>
+  <si>
+    <t>de/de/kinder-an-bord</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:25.780Z</t>
+  </si>
+  <si>
+    <t>Mit Kindern und Babys an Bord | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/kinder-an-bord</t>
+  </si>
+  <si>
+    <t>de/de/kindermenues-an-bord.report.json</t>
+  </si>
+  <si>
+    <t>de/de/kindermenues-an-bord</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:30.745Z</t>
+  </si>
+  <si>
+    <t>Kindermenüs | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/kindermenues-an-bord</t>
+  </si>
+  <si>
+    <t>de/de/lufthansa-first-class-entertainment.report.json</t>
+  </si>
+  <si>
+    <t>de/de/lufthansa-first-class-entertainment</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:02.541Z</t>
+  </si>
+  <si>
+    <t>Entertainment Welt | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/lufthansa-first-class-entertainment</t>
+  </si>
+  <si>
+    <t>de/de/lufthansa-first-class-komfort.report.json</t>
+  </si>
+  <si>
+    <t>de/de/lufthansa-first-class-komfort</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:46.333Z</t>
+  </si>
+  <si>
+    <t>Komfort an Bord der First Class | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/lufthansa-first-class-komfort</t>
+  </si>
+  <si>
+    <t>de/de/menues-auf-langstreckenfluegen.report.json</t>
+  </si>
+  <si>
+    <t>de/de/menues-auf-langstreckenfluegen</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:20.948Z</t>
+  </si>
+  <si>
+    <t>Menüs auf Langstreckenflügen | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/menues-auf-langstreckenfluegen</t>
+  </si>
+  <si>
+    <t>de/de/menues-reiseklassen.report.json</t>
+  </si>
+  <si>
+    <t>de/de/menues-reiseklassen</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:25.475Z</t>
+  </si>
+  <si>
+    <t>Menüs in unseren Reiseklassen | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/menues-reiseklassen</t>
+  </si>
+  <si>
+    <t>de/de/nav.report.json</t>
+  </si>
+  <si>
+    <t>de/de/nav</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:54:52.930Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/homepage#nav</t>
+  </si>
+  <si>
+    <t>de/de/onboard-delights-faq.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-columns"]</t>
+  </si>
+  <si>
+    <t>de/de/onboard-delights-faq</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:11.489Z</t>
+  </si>
+  <si>
+    <t>faq | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/onboard-delights-faq</t>
+  </si>
+  <si>
+    <t>de/de/onboard-delights.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-cards"]</t>
+  </si>
+  <si>
+    <t>de/de/onboard-delights</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:32.444Z</t>
+  </si>
+  <si>
+    <t>Onboard Delights | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/onboard-delights</t>
+  </si>
+  <si>
+    <t>de/de/services-an-bord.report.json</t>
+  </si>
+  <si>
+    <t>["cards-teaser","cards-teaser","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>de/de/services-an-bord</t>
+  </si>
+  <si>
+    <t>hub</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:36.688Z</t>
+  </si>
+  <si>
+    <t>Services an Bord | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/services-an-bord</t>
+  </si>
+  <si>
+    <t>de/de/speisen-und-getraenke.report.json</t>
+  </si>
+  <si>
+    <t>["columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>de/de/speisen-und-getraenke</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:10.255Z</t>
+  </si>
+  <si>
+    <t>Menüs an Bord | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/speisen-und-getraenke</t>
+  </si>
+  <si>
+    <t>de/de/unterhaltung-an-bord.report.json</t>
+  </si>
+  <si>
+    <t>de/de/unterhaltung-an-bord</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:47.115Z</t>
+  </si>
+  <si>
+    <t>Unterhaltung an Bord | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/unterhaltung-an-bord</t>
+  </si>
+  <si>
     <t>de/en/100-years.report.json</t>
   </si>
   <si>
@@ -46,13 +361,10 @@
     <t>de/en/100-years</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>campaign</t>
   </si>
   <si>
-    <t>2026-10-21T16:55:07.829Z</t>
+    <t>2026-10-21T22:34:52.969Z</t>
   </si>
   <si>
     <t>100 Years Lufthansa | Lufthansa</t>
@@ -73,7 +385,7 @@
     <t>fleet</t>
   </si>
   <si>
-    <t>2026-10-21T16:55:12.414Z</t>
+    <t>2026-10-21T22:35:08.686Z</t>
   </si>
   <si>
     <t>Airbus A350-900 | Lufthansa</t>
@@ -82,6 +394,225 @@
     <t>https://www.lufthansa.com/de/en/359</t>
   </si>
   <si>
+    <t>de/en/accessible-travel.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-cards","carousel-cards","carousel-cards"]</t>
+  </si>
+  <si>
+    <t>de/en/accessible-travel</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:47.559Z</t>
+  </si>
+  <si>
+    <t>Accessible travel | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/accessible-travel</t>
+  </si>
+  <si>
+    <t>de/en/add-sports-baggage.report.json</t>
+  </si>
+  <si>
+    <t>de/en/add-sports-baggage</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:49.905Z</t>
+  </si>
+  <si>
+    <t>Add sports baggage | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/add-sports-baggage</t>
+  </si>
+  <si>
+    <t>de/en/additional-services.report.json</t>
+  </si>
+  <si>
+    <t>de/en/additional-services</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:28:54.578Z</t>
+  </si>
+  <si>
+    <t>Extra services | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/additional-services</t>
+  </si>
+  <si>
+    <t>de/en/addresses-worldwide.report.json</t>
+  </si>
+  <si>
+    <t>de/en/addresses-worldwide</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:51.608Z</t>
+  </si>
+  <si>
+    <t>Addresses worldwide | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/addresses-worldwide</t>
+  </si>
+  <si>
+    <t>de/en/admission-rules.report.json</t>
+  </si>
+  <si>
+    <t>de/en/admission-rules</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:53.742Z</t>
+  </si>
+  <si>
+    <t>Access to our lounges | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/admission-rules</t>
+  </si>
+  <si>
+    <t>de/en/advance-seat-reservation.report.json</t>
+  </si>
+  <si>
+    <t>de/en/advance-seat-reservation</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:57.170Z</t>
+  </si>
+  <si>
+    <t>Advance seat reservation | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/advance-seat-reservation</t>
+  </si>
+  <si>
+    <t>de/en/advice-for-travellers-with-special-needs-to-and-from-the-usa.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-cards","carousel-cards"]</t>
+  </si>
+  <si>
+    <t>de/en/advice-for-travellers-with-special-needs-to-and-from-the-usa</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:59.570Z</t>
+  </si>
+  <si>
+    <t>Information about accessible travel to the USA | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/advice-for-travellers-with-special-needs-to-and-from-the-usa</t>
+  </si>
+  <si>
+    <t>de/en/affiliatemarketing.report.json</t>
+  </si>
+  <si>
+    <t>de/en/affiliatemarketing</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:02.705Z</t>
+  </si>
+  <si>
+    <t>Affiliate marketing | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/affiliatemarketing</t>
+  </si>
+  <si>
+    <t>de/en/airport-information.report.json</t>
+  </si>
+  <si>
+    <t>de/en/airport-information</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:28:57.157Z</t>
+  </si>
+  <si>
+    <t>Airport information | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/airport-information</t>
+  </si>
+  <si>
+    <t>de/en/all-check-in.report.json</t>
+  </si>
+  <si>
+    <t>de/en/all-check-in</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:05.727Z</t>
+  </si>
+  <si>
+    <t>All check-in options | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/all-check-in</t>
+  </si>
+  <si>
+    <t>de/en/arrival-services.report.json</t>
+  </si>
+  <si>
+    <t>de/en/arrival-services</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:08.819Z</t>
+  </si>
+  <si>
+    <t>Arrival services | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/arrival-services</t>
+  </si>
+  <si>
+    <t>de/en/assistenzhunde.report.json</t>
+  </si>
+  <si>
+    <t>de/en/assistenzhunde</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:11.883Z</t>
+  </si>
+  <si>
+    <t>Assistance dogs | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/assistenzhunde</t>
+  </si>
+  <si>
+    <t>de/en/automatic-check-in.report.json</t>
+  </si>
+  <si>
+    <t>de/en/automatic-check-in</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:14.648Z</t>
+  </si>
+  <si>
+    <t>Automated check-in | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/automatic-check-in</t>
+  </si>
+  <si>
+    <t>de/en/baggage-irregularities.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-columns","accordion-columns","accordion-columns"]</t>
+  </si>
+  <si>
+    <t>de/en/baggage-irregularities</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:16.983Z</t>
+  </si>
+  <si>
+    <t>Problems with baggage | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/baggage-irregularities</t>
+  </si>
+  <si>
     <t>de/en/baggage.report.json</t>
   </si>
   <si>
@@ -91,10 +622,7 @@
     <t>de/en/baggage</t>
   </si>
   <si>
-    <t>hub</t>
-  </si>
-  <si>
-    <t>2026-10-21T16:54:59.566Z</t>
+    <t>2026-10-21T22:28:51.748Z</t>
   </si>
   <si>
     <t>Baggage | Lufthansa</t>
@@ -103,6 +631,396 @@
     <t>https://www.lufthansa.com/de/en/baggage</t>
   </si>
   <si>
+    <t>de/en/bid-upgrade.report.json</t>
+  </si>
+  <si>
+    <t>de/en/bid-upgrade</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:19.821Z</t>
+  </si>
+  <si>
+    <t>Submit an offer for your upgrade | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/bid-upgrade</t>
+  </si>
+  <si>
+    <t>de/en/boarding.report.json</t>
+  </si>
+  <si>
+    <t>de/en/boarding</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:22.222Z</t>
+  </si>
+  <si>
+    <t>Boarding | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/boarding</t>
+  </si>
+  <si>
+    <t>de/en/business-class-on-short-and-medium-haul.report.json</t>
+  </si>
+  <si>
+    <t>de/en/business-class-on-short-and-medium-haul</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:03.113Z</t>
+  </si>
+  <si>
+    <t>Business Class on short and medium-haul routes | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/business-class-on-short-and-medium-haul</t>
+  </si>
+  <si>
+    <t>de/en/business-class.report.json</t>
+  </si>
+  <si>
+    <t>de/en/business-class</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:00.658Z</t>
+  </si>
+  <si>
+    <t>Business Class | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/business-class</t>
+  </si>
+  <si>
+    <t>de/en/business-services.report.json</t>
+  </si>
+  <si>
+    <t>de/en/business-services</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:05.036Z</t>
+  </si>
+  <si>
+    <t>Business Services | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/business-services</t>
+  </si>
+  <si>
+    <t>de/en/cancellations-and-refunds.report.json</t>
+  </si>
+  <si>
+    <t>de/en/cancellations-and-refunds</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:08.458Z</t>
+  </si>
+  <si>
+    <t>Cancellation and refund | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/cancellations-and-refunds</t>
+  </si>
+  <si>
+    <t>de/en/carry-on-baggage.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-columns","accordion-columns"]</t>
+  </si>
+  <si>
+    <t>de/en/carry-on-baggage</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:10.950Z</t>
+  </si>
+  <si>
+    <t>Carry-on baggage | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/carry-on-baggage</t>
+  </si>
+  <si>
+    <t>de/en/cash-and-miles.report.json</t>
+  </si>
+  <si>
+    <t>de/en/cash-and-miles</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:14.017Z</t>
+  </si>
+  <si>
+    <t>Cash &amp; Miles | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/cash-and-miles</t>
+  </si>
+  <si>
+    <t>de/en/check-in-baggage.report.json</t>
+  </si>
+  <si>
+    <t>de/en/check-in-baggage</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:16.993Z</t>
+  </si>
+  <si>
+    <t>Baggage drop | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/check-in-baggage</t>
+  </si>
+  <si>
+    <t>de/en/check-in-with-the-family.report.json</t>
+  </si>
+  <si>
+    <t>de/en/check-in-with-the-family</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:18.810Z</t>
+  </si>
+  <si>
+    <t>Online check-in with the whole family | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/check-in-with-the-family</t>
+  </si>
+  <si>
+    <t>de/en/child-restraint-systems.report.json</t>
+  </si>
+  <si>
+    <t>de/en/child-restraint-systems</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:20.992Z</t>
+  </si>
+  <si>
+    <t>Safety for small children on board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/child-restraint-systems</t>
+  </si>
+  <si>
+    <t>de/en/children-on-board.report.json</t>
+  </si>
+  <si>
+    <t>de/en/children-on-board</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:23.009Z</t>
+  </si>
+  <si>
+    <t>On board with children and babies | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/children-on-board</t>
+  </si>
+  <si>
+    <t>de/en/childrens-menus-on-board.report.json</t>
+  </si>
+  <si>
+    <t>de/en/childrens-menus-on-board</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:28.164Z</t>
+  </si>
+  <si>
+    <t>Children’s menus | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/childrens-menus-on-board</t>
+  </si>
+  <si>
+    <t>de/en/dangerous-dogs.report.json</t>
+  </si>
+  <si>
+    <t>de/en/dangerous-dogs</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:34.059Z</t>
+  </si>
+  <si>
+    <t>Fighting dog breeds and snub-nosed animals | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/dangerous-dogs</t>
+  </si>
+  <si>
+    <t>de/en/digital-baggage-services.report.json</t>
+  </si>
+  <si>
+    <t>de/en/digital-baggage-services</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:36.282Z</t>
+  </si>
+  <si>
+    <t>Digital baggage services | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/digital-baggage-services</t>
+  </si>
+  <si>
+    <t>de/en/digital-self-services.report.json</t>
+  </si>
+  <si>
+    <t>de/en/digital-self-services</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:00.047Z</t>
+  </si>
+  <si>
+    <t>Digital services | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/digital-self-services</t>
+  </si>
+  <si>
+    <t>de/en/digital-travel-companion.report.json</t>
+  </si>
+  <si>
+    <t>de/en/digital-travel-companion</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:39.166Z</t>
+  </si>
+  <si>
+    <t>Lufthansa app | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/digital-travel-companion</t>
+  </si>
+  <si>
+    <t>de/en/doctor-on-board-news.report.json</t>
+  </si>
+  <si>
+    <t>de/en/doctor-on-board-news</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:03.500Z</t>
+  </si>
+  <si>
+    <t>Doctor on Board—good to know | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/doctor-on-board-news</t>
+  </si>
+  <si>
+    <t>de/en/doctor-on-board.report.json</t>
+  </si>
+  <si>
+    <t>de/en/doctor-on-board</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:58.785Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/doctor-on-board</t>
+  </si>
+  <si>
+    <t>de/en/economy-class.report.json</t>
+  </si>
+  <si>
+    <t>de/en/economy-class</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:21.285Z</t>
+  </si>
+  <si>
+    <t>Economy Class | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/economy-class</t>
+  </si>
+  <si>
+    <t>de/en/electronic-bag-tags.report.json</t>
+  </si>
+  <si>
+    <t>de/en/electronic-bag-tags</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:23.940Z</t>
+  </si>
+  <si>
+    <t>Electronic bag tags | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/electronic-bag-tags</t>
+  </si>
+  <si>
+    <t>de/en/entryprocesses.report.json</t>
+  </si>
+  <si>
+    <t>de/en/entryprocesses</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:26.708Z</t>
+  </si>
+  <si>
+    <t>Entry regulations | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/entryprocesses</t>
+  </si>
+  <si>
+    <t>de/en/europa-tarife-economy-class.report.json</t>
+  </si>
+  <si>
+    <t>de/en/europa-tarife-economy-class</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:28.714Z</t>
+  </si>
+  <si>
+    <t>Our Europe fares | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/europa-tarife-economy-class</t>
+  </si>
+  <si>
+    <t>de/en/europcar.report.json</t>
+  </si>
+  <si>
+    <t>de/en/europcar</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:31.567Z</t>
+  </si>
+  <si>
+    <t>Europcar | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/europcar</t>
+  </si>
+  <si>
+    <t>de/en/exclusive-charter.report.json</t>
+  </si>
+  <si>
+    <t>de/en/exclusive-charter</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:33.293Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Charter | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/exclusive-charter</t>
+  </si>
+  <si>
+    <t>de/en/faq-ejournals.report.json</t>
+  </si>
+  <si>
+    <t>de/en/faq-ejournals</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:35.654Z</t>
+  </si>
+  <si>
+    <t>FAQs about eJournals | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/faq-ejournals</t>
+  </si>
+  <si>
     <t>de/en/feedback.report.json</t>
   </si>
   <si>
@@ -115,7 +1033,7 @@
     <t>form</t>
   </si>
   <si>
-    <t>2026-10-21T16:55:25.934Z</t>
+    <t>2026-10-21T22:35:24.617Z</t>
   </si>
   <si>
     <t>Feedback and other contact forms | Lufthansa</t>
@@ -124,19 +1042,184 @@
     <t>https://www.lufthansa.com/de/en/feedback</t>
   </si>
   <si>
+    <t>de/en/fia-valet-service.report.json</t>
+  </si>
+  <si>
+    <t>de/en/fia-valet-service</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:38.408Z</t>
+  </si>
+  <si>
+    <t>FIA Valet Service | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/fia-valet-service</t>
+  </si>
+  <si>
+    <t>de/en/first-class-comfort.report.json</t>
+  </si>
+  <si>
+    <t>de/en/first-class-comfort</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:43.359Z</t>
+  </si>
+  <si>
+    <t>Comfort on board First Class | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/first-class-comfort</t>
+  </si>
+  <si>
+    <t>de/en/first-class-lounges.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-columns","accordion-columns","accordion-columns","accordion-columns"]</t>
+  </si>
+  <si>
+    <t>de/en/first-class-lounges</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:48.150Z</t>
+  </si>
+  <si>
+    <t>First Class Lounges | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/first-class-lounges</t>
+  </si>
+  <si>
+    <t>de/en/first-class-personal-assistant.report.json</t>
+  </si>
+  <si>
+    <t>de/en/first-class-personal-assistant</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:49.855Z</t>
+  </si>
+  <si>
+    <t>First Class personal assistant service | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/first-class-personal-assistant</t>
+  </si>
+  <si>
+    <t>de/en/first-class-terminal.report.json</t>
+  </si>
+  <si>
+    <t>de/en/first-class-terminal</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:52.460Z</t>
+  </si>
+  <si>
+    <t>First Class Terminal | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/first-class-terminal</t>
+  </si>
+  <si>
+    <t>de/en/first-class-valet-parking-service.report.json</t>
+  </si>
+  <si>
+    <t>de/en/first-class-valet-parking-service</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:55.683Z</t>
+  </si>
+  <si>
+    <t>Valet parking service | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/first-class-valet-parking-service</t>
+  </si>
+  <si>
+    <t>de/en/first-class.report.json</t>
+  </si>
+  <si>
+    <t>de/en/first-class</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:40.870Z</t>
+  </si>
+  <si>
+    <t>Lufthansa First Class | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/first-class</t>
+  </si>
+  <si>
+    <t>de/en/fliegen-mit-baby.report.json</t>
+  </si>
+  <si>
+    <t>de/en/fliegen-mit-baby</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:58.220Z</t>
+  </si>
+  <si>
+    <t>Flying with baby | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/fliegen-mit-baby</t>
+  </si>
+  <si>
+    <t>de/en/flight-disruptions.report.json</t>
+  </si>
+  <si>
+    <t>de/en/flight-disruptions</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:00.710Z</t>
+  </si>
+  <si>
+    <t>Flights delayed and cancelled at short notice | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/flight-disruptions</t>
+  </si>
+  <si>
+    <t>de/en/flights.report.json</t>
+  </si>
+  <si>
+    <t>["columns-media"]</t>
+  </si>
+  <si>
+    <t>de/en/flights</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:04.966Z</t>
+  </si>
+  <si>
+    <t>Flight offers and destinations worldwide | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/flights</t>
+  </si>
+  <si>
+    <t>de/en/fly-more-sustainabl.report.json</t>
+  </si>
+  <si>
+    <t>de/en/fly-more-sustainabl</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:02.743Z</t>
+  </si>
+  <si>
+    <t>Fly more sustainably | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/fly-more-sustainabl</t>
+  </si>
+  <si>
     <t>de/en/flying-with-small-children.report.json</t>
   </si>
   <si>
-    <t>["accordion-columns","carousel-cards"]</t>
-  </si>
-  <si>
     <t>de/en/flying-with-small-children</t>
   </si>
   <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>2026-10-21T16:55:03.691Z</t>
+    <t>2026-10-21T22:29:44.690Z</t>
   </si>
   <si>
     <t>Flying with small children | Lufthansa</t>
@@ -145,19 +1228,172 @@
     <t>https://www.lufthansa.com/de/en/flying-with-small-children</t>
   </si>
   <si>
+    <t>de/en/flynet.report.json</t>
+  </si>
+  <si>
+    <t>de/en/flynet</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:05.112Z</t>
+  </si>
+  <si>
+    <t>FlyNet® on board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/flynet</t>
+  </si>
+  <si>
+    <t>de/en/fmg-valet-parking-service.report.json</t>
+  </si>
+  <si>
+    <t>de/en/fmg-valet-parking-service</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:07.569Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/fmg-valet-parking-service</t>
+  </si>
+  <si>
+    <t>de/en/food-and-beverages.report.json</t>
+  </si>
+  <si>
+    <t>de/en/food-and-beverages</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:08.014Z</t>
+  </si>
+  <si>
+    <t>Menus on board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/food-and-beverages</t>
+  </si>
+  <si>
+    <t>de/en/footer.report.json</t>
+  </si>
+  <si>
+    <t>de/en/footer</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:54:45.381Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/homepage#footer</t>
+  </si>
+  <si>
+    <t>de/en/free2move.report.json</t>
+  </si>
+  <si>
+    <t>de/en/free2move</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:09.325Z</t>
+  </si>
+  <si>
+    <t>Free2move carsharing | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/free2move</t>
+  </si>
+  <si>
+    <t>de/en/freigepaeck-regeln.report.json</t>
+  </si>
+  <si>
+    <t>de/en/freigepaeck-regeln</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:12.161Z</t>
+  </si>
+  <si>
+    <t>Free baggage rules at Lufthansa | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/freigepaeck-regeln</t>
+  </si>
+  <si>
+    <t>de/en/gefaehrliche-gegenstaende.report.json</t>
+  </si>
+  <si>
+    <t>de/en/gefaehrliche-gegenstaende</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:14.892Z</t>
+  </si>
+  <si>
+    <t>Dangerous goods | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/gefaehrliche-gegenstaende</t>
+  </si>
+  <si>
+    <t>de/en/green-fare.report.json</t>
+  </si>
+  <si>
+    <t>de/en/green-fare</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:16.852Z</t>
+  </si>
+  <si>
+    <t>Green Fares: More sustainable air travel | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/green-fare</t>
+  </si>
+  <si>
+    <t>de/en/group-travel-and-charter.report.json</t>
+  </si>
+  <si>
+    <t>de/en/group-travel-and-charter</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:21.847Z</t>
+  </si>
+  <si>
+    <t>Group travel and Lufthansa Charter | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/group-travel-and-charter</t>
+  </si>
+  <si>
+    <t>de/en/group-travel.report.json</t>
+  </si>
+  <si>
+    <t>de/en/group-travel</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:19.066Z</t>
+  </si>
+  <si>
+    <t>Group travel | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/group-travel</t>
+  </si>
+  <si>
+    <t>de/en/hertz.report.json</t>
+  </si>
+  <si>
+    <t>de/en/hertz</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:24.343Z</t>
+  </si>
+  <si>
+    <t>Hertz | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/hertz</t>
+  </si>
+  <si>
     <t>de/en/homepage.report.json</t>
   </si>
   <si>
-    <t>["flight-search","hero-card-overlay","fare-teaser","carousel-cards","destination-finder","cards-icon","columns-logos","accordion-columns"]</t>
-  </si>
-  <si>
     <t>de/en/homepage</t>
   </si>
   <si>
-    <t>homepage</t>
-  </si>
-  <si>
-    <t>2026-10-21T14:41:22.080Z</t>
+    <t>2026-10-21T22:28:36.795Z</t>
   </si>
   <si>
     <t>Book your flight now - travel with Lufthansa to over 200 destinations | Lufthansa</t>
@@ -166,6 +1402,21 @@
     <t>https://www.lufthansa.com/de/en/homepage</t>
   </si>
   <si>
+    <t>de/en/hotel-offers.report.json</t>
+  </si>
+  <si>
+    <t>de/en/hotel-offers</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:26.676Z</t>
+  </si>
+  <si>
+    <t>Hotel offers | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/hotel-offers</t>
+  </si>
+  <si>
     <t>de/en/imprint.report.json</t>
   </si>
   <si>
@@ -178,7 +1429,7 @@
     <t>legal</t>
   </si>
   <si>
-    <t>2026-10-21T16:55:21.743Z</t>
+    <t>2026-10-21T22:35:19.333Z</t>
   </si>
   <si>
     <t>Legal notice | Lufthansa</t>
@@ -187,6 +1438,450 @@
     <t>https://www.lufthansa.com/de/en/imprint</t>
   </si>
   <si>
+    <t>de/en/lh-rentalcar.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lh-rentalcar</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:29.136Z</t>
+  </si>
+  <si>
+    <t>Car rental partners | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lh-rentalcar</t>
+  </si>
+  <si>
+    <t>de/en/lounge-companions.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lounge-companions</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:31.893Z</t>
+  </si>
+  <si>
+    <t>Take your companions into the lounge with you | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lounge-companions</t>
+  </si>
+  <si>
+    <t>de/en/lounges.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lounges</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:12.311Z</t>
+  </si>
+  <si>
+    <t>Lounges | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lounges</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-am-flughafen-frankfurt.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-am-flughafen-frankfurt</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:33.693Z</t>
+  </si>
+  <si>
+    <t>Lufthansa at Frankfurt Airport | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-am-flughafen-frankfurt</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-at-berlin-airport.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-at-berlin-airport</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:36.028Z</t>
+  </si>
+  <si>
+    <t>Lufthansa at Berlin Brandenburg Airport | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-at-berlin-airport</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-at-duesseldorf-airport.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-at-duesseldorf-airport</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:38.951Z</t>
+  </si>
+  <si>
+    <t>Lufthansa at Dusseldorf Airport | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-at-duesseldorf-airport</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-at-vienna-airport.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-at-vienna-airport</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:41.420Z</t>
+  </si>
+  <si>
+    <t>Lufthansa at Vienna Airport | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-at-vienna-airport</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-at-zuerich-airport.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-at-zuerich-airport</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:43.859Z</t>
+  </si>
+  <si>
+    <t>Lufthansa at Zurich Airport | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-at-zuerich-airport</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-aviation-group.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-aviation-group</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:45.803Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Aviation Group | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-aviation-group</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-business-class-on-long-haul-routes.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-business-class-on-long-haul-routes</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:48.569Z</t>
+  </si>
+  <si>
+    <t>Business Class on long-haul routes | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-business-class-on-long-haul-routes</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-corporate-customers.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-corporate-customers</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:50.458Z</t>
+  </si>
+  <si>
+    <t>Lufthansa for corporate customers | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-corporate-customers</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-express-bus.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-express-bus</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:54.761Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Express Bus | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-express-bus</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-express-rail.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-express-rail</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:56.987Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Express Rail | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-express-rail</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-express.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-express</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:33:52.450Z</t>
+  </si>
+  <si>
+    <t>Airport arrival and departure – travel seamlessly | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-express</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-first-class-entertainment.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-first-class-entertainment</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:00.424Z</t>
+  </si>
+  <si>
+    <t>Entertainment world | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-first-class-entertainment</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-group-star-alliance-and-partner-airlines.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-group-star-alliance-and-partner-airlines</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:05.613Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Group, Star Alliance and partner airlines | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-group-star-alliance-and-partner-airlines</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-guide-service.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-guide-service</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:07.304Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Guide Service Munich | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-guide-service</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-terminal-muenchen.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-terminal-muenchen</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:10.267Z</t>
+  </si>
+  <si>
+    <t>Lufthansa at Munich Airport | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-terminal-muenchen</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-travel-classes.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lufthansa-travel-classes</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:15.410Z</t>
+  </si>
+  <si>
+    <t>Our travel classes | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lufthansa-travel-classes</t>
+  </si>
+  <si>
+    <t>de/en/medikamenten-transport.report.json</t>
+  </si>
+  <si>
+    <t>de/en/medikamenten-transport</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:13.158Z</t>
+  </si>
+  <si>
+    <t>Always at the right temperature | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/medikamenten-transport</t>
+  </si>
+  <si>
+    <t>de/en/meetings-and-events-delegates.report.json</t>
+  </si>
+  <si>
+    <t>de/en/meetings-and-events-delegates</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:15.050Z</t>
+  </si>
+  <si>
+    <t>Meetings &amp; Events: Information for organisers | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/meetings-and-events-delegates</t>
+  </si>
+  <si>
+    <t>de/en/meetings-and-events-organisers.report.json</t>
+  </si>
+  <si>
+    <t>de/en/meetings-and-events-organisers</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:16.965Z</t>
+  </si>
+  <si>
+    <t>Meeting &amp; Events: Information for organisers | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/meetings-and-events-organisers</t>
+  </si>
+  <si>
+    <t>de/en/meetings-and-events.report.json</t>
+  </si>
+  <si>
+    <t>de/en/meetings-and-events</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:17.390Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Group Meetings &amp; Events | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/meetings-and-events</t>
+  </si>
+  <si>
+    <t>de/en/menus-on-long-haul-flights.report.json</t>
+  </si>
+  <si>
+    <t>de/en/menus-on-long-haul-flights</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:18.943Z</t>
+  </si>
+  <si>
+    <t>Menus on long-haul flights | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/menus-on-long-haul-flights</t>
+  </si>
+  <si>
+    <t>de/en/menus-travel-classes.report.json</t>
+  </si>
+  <si>
+    <t>de/en/menus-travel-classes</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:23.793Z</t>
+  </si>
+  <si>
+    <t>Menus in our travel classes | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/menus-travel-classes</t>
+  </si>
+  <si>
+    <t>de/en/miles-and-more.report.json</t>
+  </si>
+  <si>
+    <t>de/en/miles-and-more</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:19.875Z</t>
+  </si>
+  <si>
+    <t>Miles &amp; More – Our frequent flyer programme | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/miles-and-more</t>
+  </si>
+  <si>
+    <t>de/en/mobility-partner-program-healthcare.report.json</t>
+  </si>
+  <si>
+    <t>de/en/mobility-partner-program-healthcare</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:27.573Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Global Healthcare and Medical Services | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/mobility-partner-program-healthcare</t>
+  </si>
+  <si>
+    <t>de/en/nav.report.json</t>
+  </si>
+  <si>
+    <t>de/en/nav</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:54:40.832Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/homepage#nav</t>
+  </si>
+  <si>
+    <t>de/en/onboard-delights.report.json</t>
+  </si>
+  <si>
+    <t>de/en/onboard-delights</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:30.374Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/onboard-delights</t>
+  </si>
+  <si>
+    <t>de/en/online-check-in-info.report.json</t>
+  </si>
+  <si>
+    <t>de/en/online-check-in-info</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:34.662Z</t>
+  </si>
+  <si>
+    <t>Online check-in information | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/online-check-in-info</t>
+  </si>
+  <si>
     <t>de/en/online-check-in.report.json</t>
   </si>
   <si>
@@ -199,7 +1894,7 @@
     <t>app-entry</t>
   </si>
   <si>
-    <t>2026-10-21T16:55:30.108Z</t>
+    <t>2026-10-21T22:35:29.211Z</t>
   </si>
   <si>
     <t>Online check-in | Lufthansa</t>
@@ -208,6 +1903,486 @@
     <t>https://www.lufthansa.com/de/en/online-check-in</t>
   </si>
   <si>
+    <t>de/en/overview-flights.report.json</t>
+  </si>
+  <si>
+    <t>de/en/overview-flights</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:22.394Z</t>
+  </si>
+  <si>
+    <t>Flights – your journey starts here | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/overview-flights</t>
+  </si>
+  <si>
+    <t>de/en/overview-manage.report.json</t>
+  </si>
+  <si>
+    <t>["cards-teaser","cards-teaser","cards-teaser","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>de/en/overview-manage</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:24.956Z</t>
+  </si>
+  <si>
+    <t>Manage your bookings | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/overview-manage</t>
+  </si>
+  <si>
+    <t>de/en/overview-special-request.report.json</t>
+  </si>
+  <si>
+    <t>de/en/overview-special-request</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:26.725Z</t>
+  </si>
+  <si>
+    <t>Special requests | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/overview-special-request</t>
+  </si>
+  <si>
+    <t>de/en/overview-travel-information.report.json</t>
+  </si>
+  <si>
+    <t>de/en/overview-travel-information</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:29.135Z</t>
+  </si>
+  <si>
+    <t>Travel information – what you need to know | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/overview-travel-information</t>
+  </si>
+  <si>
+    <t>de/en/partner.report.json</t>
+  </si>
+  <si>
+    <t>de/en/partner</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:37.659Z</t>
+  </si>
+  <si>
+    <t>Partners | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/partner</t>
+  </si>
+  <si>
+    <t>de/en/passenger-receipt-90.report.json</t>
+  </si>
+  <si>
+    <t>de/en/passenger-receipt-90</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:39.755Z</t>
+  </si>
+  <si>
+    <t>Passenger receipt | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/passenger-receipt-90</t>
+  </si>
+  <si>
+    <t>de/en/passengers-using-wheelchairs.report.json</t>
+  </si>
+  <si>
+    <t>de/en/passengers-using-wheelchairs</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:42.001Z</t>
+  </si>
+  <si>
+    <t>Passengers requiring wheelchairs | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/passengers-using-wheelchairs</t>
+  </si>
+  <si>
+    <t>de/en/services-at-the-airport.report.json</t>
+  </si>
+  <si>
+    <t>de/en/services-at-the-airport</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:32.371Z</t>
+  </si>
+  <si>
+    <t>Services at the airport | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/services-at-the-airport</t>
+  </si>
+  <si>
+    <t>de/en/services-on-board.report.json</t>
+  </si>
+  <si>
+    <t>de/en/services-on-board</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:34.558Z</t>
+  </si>
+  <si>
+    <t>Services on board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/services-on-board</t>
+  </si>
+  <si>
+    <t>de/en/special-needs.report.json</t>
+  </si>
+  <si>
+    <t>de/en/special-needs</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:29:39.318Z</t>
+  </si>
+  <si>
+    <t>Register your assistance requirements online | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/special-needs</t>
+  </si>
+  <si>
+    <t>de/en/timetable-and-flight-status.report.json</t>
+  </si>
+  <si>
+    <t>["flight-status","columns-media","columns-media","columns-media","accordion-columns"]</t>
+  </si>
+  <si>
+    <t>de/en/timetable-and-flight-status</t>
+  </si>
+  <si>
+    <t>flight-status</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:01:33.445Z</t>
+  </si>
+  <si>
+    <t>Timetable &amp; flight status | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/timetable-and-flight-status</t>
+  </si>
+  <si>
+    <t>de/en/unterhaltung-an-bord.report.json</t>
+  </si>
+  <si>
+    <t>de/en/unterhaltung-an-bord</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:44.190Z</t>
+  </si>
+  <si>
+    <t>Entertainment on board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/unterhaltung-an-bord</t>
+  </si>
+  <si>
+    <t>gb/en/footer.report.json</t>
+  </si>
+  <si>
+    <t>gb/en/footer</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:55:19.112Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/gb/en/homepage#footer</t>
+  </si>
+  <si>
+    <t>gb/en/homepage.report.json</t>
+  </si>
+  <si>
+    <t>gb/en/homepage</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:28:46.096Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/gb/en/homepage</t>
+  </si>
+  <si>
+    <t>gb/en/nav.report.json</t>
+  </si>
+  <si>
+    <t>gb/en/nav</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:55:14.658Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/gb/en/homepage#nav</t>
+  </si>
+  <si>
+    <t>lhg/de/en.report.json</t>
+  </si>
+  <si>
+    <t>["flight-search","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price","cards-price"]</t>
+  </si>
+  <si>
+    <t>lhg/de/en</t>
+  </si>
+  <si>
+    <t>aircore-destination-overview</t>
+  </si>
+  <si>
+    <t>2026-10-21T16:55:43.571Z</t>
+  </si>
+  <si>
+    <t>Book flights to destinations all over the world | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/lhg/de/en</t>
+  </si>
+  <si>
+    <t>at/de/fragments/payment-social.report.json</t>
+  </si>
+  <si>
+    <t>payment-social</t>
+  </si>
+  <si>
+    <t>at/de/fragments/payment-social</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:55:10.878Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/at/de/homepage#payment-social</t>
+  </si>
+  <si>
+    <t>de/de/discover-lufthansa/new-onboard-experience.report.json</t>
+  </si>
+  <si>
+    <t>["hero-campaign","hero-campaign","hero-campaign","hero-campaign","hero-campaign","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>de/de/discover-lufthansa/new-onboard-experience</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:35:03.116Z</t>
+  </si>
+  <si>
+    <t>New Onboard Experience | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/discover-lufthansa/new-onboard-experience</t>
+  </si>
+  <si>
+    <t>de/de/during-your-trip/lhg-wifi.report.json</t>
+  </si>
+  <si>
+    <t>de/de/during-your-trip/lhg-wifi</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:18.873Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Group Wi-Fi | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/during-your-trip/lhg-wifi</t>
+  </si>
+  <si>
+    <t>de/de/fragments/payment-social.report.json</t>
+  </si>
+  <si>
+    <t>de/de/fragments/payment-social</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:54:59.638Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/homepage#payment-social</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/pax-receipt.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/pax-receipt</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:46.923Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/pax-receipt</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/rebook.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/rebook</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:52.704Z</t>
+  </si>
+  <si>
+    <t>Flight Rebooking | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/rebook</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/flightreservation-priceguarantee.report.json</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/flightreservation-priceguarantee</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:51.511Z</t>
+  </si>
+  <si>
+    <t>Reservation with price guarantee | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/discover-lufthansa/flightreservation-priceguarantee</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/miles-and-more-credit-card.report.json</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/miles-and-more-credit-card</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:56.206Z</t>
+  </si>
+  <si>
+    <t>Miles &amp; More Credit Card | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/discover-lufthansa/miles-and-more-credit-card</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/new-onboard-experience.report.json</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/new-onboard-experience</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:59.894Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/discover-lufthansa/new-onboard-experience</t>
+  </si>
+  <si>
+    <t>de/en/during-your-trip/internet-overview.report.json</t>
+  </si>
+  <si>
+    <t>de/en/during-your-trip/internet-overview</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:14.040Z</t>
+  </si>
+  <si>
+    <t>Internet | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/during-your-trip/internet-overview</t>
+  </si>
+  <si>
+    <t>de/en/during-your-trip/lhg-wifi.report.json</t>
+  </si>
+  <si>
+    <t>de/en/during-your-trip/lhg-wifi</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:16.809Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/during-your-trip/lhg-wifi</t>
+  </si>
+  <si>
+    <t>de/en/fragments/payment-social.report.json</t>
+  </si>
+  <si>
+    <t>de/en/fragments/payment-social</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:54:49.651Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/homepage#payment-social</t>
+  </si>
+  <si>
+    <t>gb/en/fragments/payment-social.report.json</t>
+  </si>
+  <si>
+    <t>gb/en/fragments/payment-social</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:55:24.929Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/gb/en/homepage#payment-social</t>
+  </si>
+  <si>
+    <t>lhg/de/en/zz-test.report.json</t>
+  </si>
+  <si>
+    <t>["cards-icon-text"]</t>
+  </si>
+  <si>
+    <t>lhg/de/en/zz-test</t>
+  </si>
+  <si>
+    <t>aircore-destination</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:04:36.900Z</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/lhg/de/en/zz-test</t>
+  </si>
+  <si>
+    <t>de/de/100-years/history/menu-on-board.report.json</t>
+  </si>
+  <si>
+    <t>["hero-campaign","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>de/de/100-years/history/menu-on-board</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:57.145Z</t>
+  </si>
+  <si>
+    <t>Menüs an Board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/de/100-years/history/menu-on-board</t>
+  </si>
+  <si>
+    <t>de/en/100-years/history/menu-on-board.report.json</t>
+  </si>
+  <si>
+    <t>de/en/100-years/history/menu-on-board</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:34:54.910Z</t>
+  </si>
+  <si>
+    <t>Menus on Board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/100-years/history/menu-on-board</t>
+  </si>
+  <si>
     <t>de/en/articles/explore-the-world/eat-see-do-berlin.report.json</t>
   </si>
   <si>
@@ -220,13 +2395,340 @@
     <t>insights</t>
   </si>
   <si>
-    <t>2026-10-21T16:55:17.564Z</t>
-  </si>
-  <si>
-    <t/>
+    <t>2026-10-21T22:35:13.632Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/articles/explore-the-world/eat-see-do-berlin</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/additional-services/get-your-guide.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/additional-services/get-your-guide</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:23.858Z</t>
+  </si>
+  <si>
+    <t>Unforgettable travel experiences—GetYourGuide | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/additional-services/get-your-guide</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/additional-services/travel-insurances.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/additional-services/travel-insurances</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:26.033Z</t>
+  </si>
+  <si>
+    <t>Travel Care | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/additional-services/travel-insurances</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/digital-self-services/airline-apps.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/digital-self-services/airline-apps</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:27.759Z</t>
+  </si>
+  <si>
+    <t>Simply travel smarter | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/digital-self-services/airline-apps</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/air-baltic.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/air-baltic</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:30.294Z</t>
+  </si>
+  <si>
+    <t>Your Lufthansa flight with airBaltic | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/flights/air-baltic</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/ana.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/ana</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:32.649Z</t>
+  </si>
+  <si>
+    <t>ANA | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/flights/ana</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/giftvoucher.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-columns","carousel-cards","carousel-cards"]</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/giftvoucher</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:37.799Z</t>
+  </si>
+  <si>
+    <t>Buy a Lufthansa Gift Card &amp; give a flight as a gift | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/flights/giftvoucher</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/helvetic.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/helvetic</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:40.563Z</t>
+  </si>
+  <si>
+    <t>Helvetic | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/flights/helvetic</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/lufthansa-voucher.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/lufthansa-voucher</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:43.081Z</t>
+  </si>
+  <si>
+    <t>Terms of use for the purchase of Gift Vouchers | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/flights/lufthansa-voucher</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/wetlease-hub.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/wetlease-hub</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:44.869Z</t>
+  </si>
+  <si>
+    <t>Wet lease flights | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/flights/wetlease-hub</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/pax-receipt/invoices-different-countries.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/pax-receipt/invoices-different-countries</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:49.989Z</t>
+  </si>
+  <si>
+    <t>Invoices for different countries | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/pax-receipt/invoices-different-countries</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/rebook/involuntary-rebooking.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/rebook/involuntary-rebooking</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:55.679Z</t>
+  </si>
+  <si>
+    <t>Flight cancellation | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/rebook/involuntary-rebooking</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/rebook/voluntary-rebooking.report.json</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/rebook/voluntary-rebooking</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:57.574Z</t>
+  </si>
+  <si>
+    <t>Change flight | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/rebook/voluntary-rebooking</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/carbon-offsetting/climate-protection-projects.report.json</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/carbon-offsetting/climate-protection-projects</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:42.262Z</t>
+  </si>
+  <si>
+    <t>Climate protection projects | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/discover-lufthansa/carbon-offsetting/climate-protection-projects</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/carbon-offsetting/environmental-cost-surcharge.report.json</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/carbon-offsetting/environmental-cost-surcharge</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:44.526Z</t>
+  </si>
+  <si>
+    <t>Environmental Cost Surcharge | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/discover-lufthansa/carbon-offsetting/environmental-cost-surcharge</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/carbon-offsetting/faq-saf.report.json</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/carbon-offsetting/faq-saf</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:47.219Z</t>
+  </si>
+  <si>
+    <t>FAQs Sustainable Aviation Fuel | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/discover-lufthansa/carbon-offsetting/faq-saf</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/carbon-offsetting/saf.report.json</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/carbon-offsetting/saf</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:49.735Z</t>
+  </si>
+  <si>
+    <t>Why support the use of Sustainable Aviation Fuel? | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/discover-lufthansa/carbon-offsetting/saf</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/lufthansa-group-airlines/ita-airways.report.json</t>
+  </si>
+  <si>
+    <t>de/en/discover-lufthansa/lufthansa-group-airlines/ita-airways</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:31:53.994Z</t>
+  </si>
+  <si>
+    <t>ITA Airways | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/discover-lufthansa/lufthansa-group-airlines/ita-airways</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/ana/faq.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-columns","accordion-columns","accordion-columns","accordion-columns","accordion-columns","accordion-columns"]</t>
+  </si>
+  <si>
+    <t>de/en/book-and-manage/flights/ana/faq</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:30:35.269Z</t>
+  </si>
+  <si>
+    <t>FAQs on travel with Lufthansa and ANA | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/book-and-manage/flights/ana/faq</t>
+  </si>
+  <si>
+    <t>de/en/during-your-trip/food-and-beverages/onboard-delights/faq.report.json</t>
+  </si>
+  <si>
+    <t>de/en/during-your-trip/food-and-beverages/onboard-delights/faq</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:32:08.618Z</t>
+  </si>
+  <si>
+    <t>FAQs | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/during-your-trip/food-and-beverages/onboard-delights/faq</t>
+  </si>
+  <si>
+    <t>lhg/de/en/dest/cy/new-york.report.json</t>
+  </si>
+  <si>
+    <t>["flight-search","cards-price","accordion-columns","accordion-columns","table-deals","cards-icon-text","weather","accordion-side-by-side"]</t>
+  </si>
+  <si>
+    <t>lhg/de/en/dest/cy/new-york</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:07:20.550Z</t>
+  </si>
+  <si>
+    <t>Flight to New York (NYC) | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/lhg/de/en/dest/cy/new-york</t>
+  </si>
+  <si>
+    <t>lhg/de/en/o-d/c-c/germany-usa.report.json</t>
+  </si>
+  <si>
+    <t>["flight-search","cards-icon-text","accordion-columns","accordion-side-by-side"]</t>
+  </si>
+  <si>
+    <t>lhg/de/en/o-d/c-c/germany-usa</t>
+  </si>
+  <si>
+    <t>aircore-route</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:07:24.799Z</t>
+  </si>
+  <si>
+    <t>Flights from Germany to USA | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/lhg/de/en/o-d/c-c/germany-usa</t>
   </si>
 </sst>
 </file>
@@ -615,16 +3117,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="50" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="9" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,48 +3153,54 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -701,191 +3211,5000 @@
       <c r="H3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" t="s">
+        <v>117</v>
+      </c>
+      <c r="H21" t="s">
+        <v>118</v>
+      </c>
+      <c r="I21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" t="s">
+        <v>125</v>
+      </c>
+      <c r="I22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" t="s">
+        <v>141</v>
+      </c>
+      <c r="I25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" t="s">
+        <v>146</v>
+      </c>
+      <c r="I26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" t="s">
+        <v>151</v>
+      </c>
+      <c r="I27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" t="s">
+        <v>155</v>
+      </c>
+      <c r="H28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" t="s">
+        <v>167</v>
+      </c>
+      <c r="I30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" t="s">
+        <v>177</v>
+      </c>
+      <c r="I32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>180</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" t="s">
+        <v>182</v>
+      </c>
+      <c r="I33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" t="s">
+        <v>187</v>
+      </c>
+      <c r="I34" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>190</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" t="s">
+        <v>191</v>
+      </c>
+      <c r="H35" t="s">
+        <v>192</v>
+      </c>
+      <c r="I35" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>196</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>197</v>
+      </c>
+      <c r="H36" t="s">
+        <v>198</v>
+      </c>
+      <c r="I36" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>200</v>
+      </c>
+      <c r="B37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
+        <v>98</v>
+      </c>
+      <c r="G37" t="s">
+        <v>203</v>
+      </c>
+      <c r="H37" t="s">
+        <v>204</v>
+      </c>
+      <c r="I37" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>207</v>
+      </c>
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" t="s">
+        <v>208</v>
+      </c>
+      <c r="H38" t="s">
+        <v>209</v>
+      </c>
+      <c r="I38" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>211</v>
+      </c>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>212</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" t="s">
+        <v>213</v>
+      </c>
+      <c r="H39" t="s">
+        <v>214</v>
+      </c>
+      <c r="I39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>217</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" t="s">
+        <v>218</v>
+      </c>
+      <c r="H40" t="s">
+        <v>219</v>
+      </c>
+      <c r="I40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>222</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" t="s">
+        <v>223</v>
+      </c>
+      <c r="H41" t="s">
+        <v>224</v>
+      </c>
+      <c r="I41" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>226</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>227</v>
+      </c>
+      <c r="E42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42" t="s">
+        <v>228</v>
+      </c>
+      <c r="H42" t="s">
+        <v>229</v>
+      </c>
+      <c r="I42" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>231</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>232</v>
+      </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" t="s">
+        <v>233</v>
+      </c>
+      <c r="H43" t="s">
+        <v>234</v>
+      </c>
+      <c r="I43" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" t="s">
+        <v>237</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>238</v>
+      </c>
+      <c r="E44" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44" t="s">
+        <v>239</v>
+      </c>
+      <c r="H44" t="s">
+        <v>240</v>
+      </c>
+      <c r="I44" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>242</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>243</v>
+      </c>
+      <c r="E45" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" t="s">
+        <v>244</v>
+      </c>
+      <c r="H45" t="s">
+        <v>245</v>
+      </c>
+      <c r="I45" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>247</v>
+      </c>
+      <c r="B46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" t="s">
+        <v>249</v>
+      </c>
+      <c r="H46" t="s">
+        <v>250</v>
+      </c>
+      <c r="I46" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>252</v>
+      </c>
+      <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" t="s">
+        <v>254</v>
+      </c>
+      <c r="H47" t="s">
+        <v>255</v>
+      </c>
+      <c r="I47" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>258</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" t="s">
+        <v>259</v>
+      </c>
+      <c r="H48" t="s">
+        <v>260</v>
+      </c>
+      <c r="I48" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>262</v>
+      </c>
+      <c r="B49" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
+        <v>263</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" t="s">
+        <v>264</v>
+      </c>
+      <c r="H49" t="s">
+        <v>265</v>
+      </c>
+      <c r="I49" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" t="s">
+        <v>268</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" t="s">
+        <v>269</v>
+      </c>
+      <c r="H50" t="s">
+        <v>270</v>
+      </c>
+      <c r="I50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
+        <v>273</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" t="s">
+        <v>274</v>
+      </c>
+      <c r="H51" t="s">
+        <v>275</v>
+      </c>
+      <c r="I51" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>278</v>
+      </c>
+      <c r="E52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52" t="s">
+        <v>279</v>
+      </c>
+      <c r="H52" t="s">
+        <v>280</v>
+      </c>
+      <c r="I52" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>283</v>
+      </c>
+      <c r="E53" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" t="s">
+        <v>98</v>
+      </c>
+      <c r="G53" t="s">
+        <v>284</v>
+      </c>
+      <c r="H53" t="s">
+        <v>285</v>
+      </c>
+      <c r="I53" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>287</v>
+      </c>
+      <c r="B54" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>288</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" t="s">
+        <v>289</v>
+      </c>
+      <c r="H54" t="s">
+        <v>290</v>
+      </c>
+      <c r="I54" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>292</v>
+      </c>
+      <c r="B55" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55" t="s">
+        <v>294</v>
+      </c>
+      <c r="H55" t="s">
+        <v>295</v>
+      </c>
+      <c r="I55" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>297</v>
+      </c>
+      <c r="B56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" t="s">
+        <v>298</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" t="s">
+        <v>299</v>
+      </c>
+      <c r="H56" t="s">
+        <v>39</v>
+      </c>
+      <c r="I56" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>301</v>
+      </c>
+      <c r="B57" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" t="s">
+        <v>302</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" t="s">
+        <v>303</v>
+      </c>
+      <c r="H57" t="s">
+        <v>304</v>
+      </c>
+      <c r="I57" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>306</v>
+      </c>
+      <c r="B58" t="s">
+        <v>84</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>307</v>
+      </c>
+      <c r="E58" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" t="s">
+        <v>308</v>
+      </c>
+      <c r="H58" t="s">
+        <v>309</v>
+      </c>
+      <c r="I58" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>311</v>
+      </c>
+      <c r="B59" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>312</v>
+      </c>
+      <c r="E59" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" t="s">
+        <v>313</v>
+      </c>
+      <c r="H59" t="s">
+        <v>314</v>
+      </c>
+      <c r="I59" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>316</v>
+      </c>
+      <c r="B60" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" t="s">
+        <v>317</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" t="s">
+        <v>318</v>
+      </c>
+      <c r="H60" t="s">
+        <v>319</v>
+      </c>
+      <c r="I60" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>321</v>
+      </c>
+      <c r="B61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>322</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61" t="s">
+        <v>323</v>
+      </c>
+      <c r="H61" t="s">
+        <v>324</v>
+      </c>
+      <c r="I61" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>326</v>
+      </c>
+      <c r="B62" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" t="s">
+        <v>327</v>
+      </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
+        <v>31</v>
+      </c>
+      <c r="G62" t="s">
+        <v>328</v>
+      </c>
+      <c r="H62" t="s">
+        <v>329</v>
+      </c>
+      <c r="I62" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>331</v>
+      </c>
+      <c r="B63" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>332</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" t="s">
+        <v>333</v>
+      </c>
+      <c r="H63" t="s">
+        <v>334</v>
+      </c>
+      <c r="I63" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>336</v>
+      </c>
+      <c r="B64" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" t="s">
+        <v>338</v>
+      </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" t="s">
+        <v>339</v>
+      </c>
+      <c r="G64" t="s">
+        <v>340</v>
+      </c>
+      <c r="H64" t="s">
+        <v>341</v>
+      </c>
+      <c r="I64" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>343</v>
+      </c>
+      <c r="B65" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" t="s">
+        <v>344</v>
+      </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" t="s">
+        <v>345</v>
+      </c>
+      <c r="H65" t="s">
+        <v>346</v>
+      </c>
+      <c r="I65" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>348</v>
+      </c>
+      <c r="B66" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>349</v>
+      </c>
+      <c r="E66" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" t="s">
+        <v>350</v>
+      </c>
+      <c r="H66" t="s">
+        <v>351</v>
+      </c>
+      <c r="I66" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>353</v>
+      </c>
+      <c r="B67" t="s">
+        <v>354</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" t="s">
+        <v>355</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" t="s">
+        <v>356</v>
+      </c>
+      <c r="H67" t="s">
+        <v>357</v>
+      </c>
+      <c r="I67" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>359</v>
+      </c>
+      <c r="B68" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" t="s">
+        <v>360</v>
+      </c>
+      <c r="E68" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" t="s">
+        <v>361</v>
+      </c>
+      <c r="H68" t="s">
+        <v>362</v>
+      </c>
+      <c r="I68" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>364</v>
+      </c>
+      <c r="B69" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" t="s">
+        <v>365</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69" t="s">
+        <v>366</v>
+      </c>
+      <c r="H69" t="s">
+        <v>367</v>
+      </c>
+      <c r="I69" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>369</v>
+      </c>
+      <c r="B70" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>370</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" t="s">
+        <v>371</v>
+      </c>
+      <c r="H70" t="s">
+        <v>372</v>
+      </c>
+      <c r="I70" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>374</v>
+      </c>
+      <c r="B71" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" t="s">
+        <v>375</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" t="s">
+        <v>376</v>
+      </c>
+      <c r="H71" t="s">
+        <v>377</v>
+      </c>
+      <c r="I71" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>379</v>
+      </c>
+      <c r="B72" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" t="s">
+        <v>380</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>31</v>
+      </c>
+      <c r="G72" t="s">
+        <v>381</v>
+      </c>
+      <c r="H72" t="s">
+        <v>382</v>
+      </c>
+      <c r="I72" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>384</v>
+      </c>
+      <c r="B73" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" t="s">
+        <v>385</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73" t="s">
+        <v>386</v>
+      </c>
+      <c r="H73" t="s">
+        <v>387</v>
+      </c>
+      <c r="I73" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>389</v>
+      </c>
+      <c r="B74" t="s">
+        <v>390</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" t="s">
+        <v>391</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>98</v>
+      </c>
+      <c r="G74" t="s">
+        <v>392</v>
+      </c>
+      <c r="H74" t="s">
+        <v>393</v>
+      </c>
+      <c r="I74" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>395</v>
+      </c>
+      <c r="B75" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" t="s">
+        <v>396</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" t="s">
+        <v>31</v>
+      </c>
+      <c r="G75" t="s">
+        <v>397</v>
+      </c>
+      <c r="H75" t="s">
+        <v>398</v>
+      </c>
+      <c r="I75" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>400</v>
+      </c>
+      <c r="B76" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" t="s">
+        <v>401</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
+        <v>31</v>
+      </c>
+      <c r="G76" t="s">
+        <v>402</v>
+      </c>
+      <c r="H76" t="s">
+        <v>403</v>
+      </c>
+      <c r="I76" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>405</v>
+      </c>
+      <c r="B77" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" t="s">
+        <v>406</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>31</v>
+      </c>
+      <c r="G77" t="s">
+        <v>407</v>
+      </c>
+      <c r="H77" t="s">
+        <v>408</v>
+      </c>
+      <c r="I77" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>410</v>
+      </c>
+      <c r="B78" t="s">
+        <v>36</v>
+      </c>
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" t="s">
+        <v>411</v>
+      </c>
+      <c r="E78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" t="s">
+        <v>31</v>
+      </c>
+      <c r="G78" t="s">
+        <v>412</v>
+      </c>
+      <c r="H78" t="s">
+        <v>372</v>
+      </c>
+      <c r="I78" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>414</v>
+      </c>
+      <c r="B79" t="s">
+        <v>103</v>
+      </c>
+      <c r="C79" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" t="s">
+        <v>415</v>
+      </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>98</v>
+      </c>
+      <c r="G79" t="s">
+        <v>416</v>
+      </c>
+      <c r="H79" t="s">
+        <v>417</v>
+      </c>
+      <c r="I79" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>419</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="D80" t="s">
+        <v>420</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>421</v>
+      </c>
+      <c r="H80" t="s">
+        <v>10</v>
+      </c>
+      <c r="I80" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>423</v>
+      </c>
+      <c r="B81" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" t="s">
+        <v>424</v>
+      </c>
+      <c r="E81" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" t="s">
+        <v>31</v>
+      </c>
+      <c r="G81" t="s">
+        <v>425</v>
+      </c>
+      <c r="H81" t="s">
+        <v>426</v>
+      </c>
+      <c r="I81" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>428</v>
+      </c>
+      <c r="B82" t="s">
+        <v>237</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" t="s">
+        <v>429</v>
+      </c>
+      <c r="E82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" t="s">
+        <v>31</v>
+      </c>
+      <c r="G82" t="s">
+        <v>430</v>
+      </c>
+      <c r="H82" t="s">
+        <v>431</v>
+      </c>
+      <c r="I82" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>433</v>
+      </c>
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" t="s">
+        <v>434</v>
+      </c>
+      <c r="E83" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" t="s">
+        <v>31</v>
+      </c>
+      <c r="G83" t="s">
+        <v>435</v>
+      </c>
+      <c r="H83" t="s">
+        <v>436</v>
+      </c>
+      <c r="I83" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>438</v>
+      </c>
+      <c r="B84" t="s">
+        <v>36</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" t="s">
+        <v>439</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
+        <v>31</v>
+      </c>
+      <c r="G84" t="s">
+        <v>440</v>
+      </c>
+      <c r="H84" t="s">
+        <v>441</v>
+      </c>
+      <c r="I84" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>443</v>
+      </c>
+      <c r="B85" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" t="s">
+        <v>444</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
+        <v>31</v>
+      </c>
+      <c r="G85" t="s">
+        <v>445</v>
+      </c>
+      <c r="H85" t="s">
+        <v>446</v>
+      </c>
+      <c r="I85" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>448</v>
+      </c>
+      <c r="B86" t="s">
+        <v>84</v>
+      </c>
+      <c r="C86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" t="s">
+        <v>449</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" t="s">
+        <v>31</v>
+      </c>
+      <c r="G86" t="s">
+        <v>450</v>
+      </c>
+      <c r="H86" t="s">
+        <v>451</v>
+      </c>
+      <c r="I86" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>453</v>
+      </c>
+      <c r="B87" t="s">
+        <v>36</v>
+      </c>
+      <c r="C87" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" t="s">
+        <v>454</v>
+      </c>
+      <c r="E87" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" t="s">
+        <v>31</v>
+      </c>
+      <c r="G87" t="s">
+        <v>455</v>
+      </c>
+      <c r="H87" t="s">
+        <v>456</v>
+      </c>
+      <c r="I87" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>458</v>
+      </c>
+      <c r="B88" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" t="s">
+        <v>459</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" t="s">
+        <v>460</v>
+      </c>
+      <c r="H88" t="s">
+        <v>461</v>
+      </c>
+      <c r="I88" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>463</v>
+      </c>
+      <c r="B89" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" t="s">
+        <v>464</v>
+      </c>
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>31</v>
+      </c>
+      <c r="G89" t="s">
+        <v>465</v>
+      </c>
+      <c r="H89" t="s">
+        <v>466</v>
+      </c>
+      <c r="I89" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>468</v>
+      </c>
+      <c r="B90" t="s">
+        <v>469</v>
+      </c>
+      <c r="C90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" t="s">
+        <v>470</v>
+      </c>
+      <c r="E90" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" t="s">
+        <v>471</v>
+      </c>
+      <c r="G90" t="s">
+        <v>472</v>
+      </c>
+      <c r="H90" t="s">
+        <v>473</v>
+      </c>
+      <c r="I90" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>475</v>
+      </c>
+      <c r="B91" t="s">
+        <v>36</v>
+      </c>
+      <c r="C91" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" t="s">
+        <v>476</v>
+      </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" t="s">
+        <v>31</v>
+      </c>
+      <c r="G91" t="s">
+        <v>477</v>
+      </c>
+      <c r="H91" t="s">
+        <v>478</v>
+      </c>
+      <c r="I91" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>480</v>
+      </c>
+      <c r="B92" t="s">
+        <v>36</v>
+      </c>
+      <c r="C92" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" t="s">
+        <v>481</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
+        <v>31</v>
+      </c>
+      <c r="G92" t="s">
+        <v>482</v>
+      </c>
+      <c r="H92" t="s">
+        <v>483</v>
+      </c>
+      <c r="I92" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>485</v>
+      </c>
+      <c r="B93" t="s">
+        <v>390</v>
+      </c>
+      <c r="C93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" t="s">
+        <v>486</v>
+      </c>
+      <c r="E93" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" t="s">
+        <v>98</v>
+      </c>
+      <c r="G93" t="s">
+        <v>487</v>
+      </c>
+      <c r="H93" t="s">
+        <v>488</v>
+      </c>
+      <c r="I93" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>490</v>
+      </c>
+      <c r="B94" t="s">
+        <v>36</v>
+      </c>
+      <c r="C94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" t="s">
+        <v>491</v>
+      </c>
+      <c r="E94" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" t="s">
+        <v>31</v>
+      </c>
+      <c r="G94" t="s">
+        <v>492</v>
+      </c>
+      <c r="H94" t="s">
+        <v>493</v>
+      </c>
+      <c r="I94" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>495</v>
+      </c>
+      <c r="B95" t="s">
+        <v>36</v>
+      </c>
+      <c r="C95" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" t="s">
+        <v>496</v>
+      </c>
+      <c r="E95" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" t="s">
+        <v>31</v>
+      </c>
+      <c r="G95" t="s">
+        <v>497</v>
+      </c>
+      <c r="H95" t="s">
+        <v>498</v>
+      </c>
+      <c r="I95" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>500</v>
+      </c>
+      <c r="B96" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" t="s">
+        <v>501</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" t="s">
+        <v>31</v>
+      </c>
+      <c r="G96" t="s">
+        <v>502</v>
+      </c>
+      <c r="H96" t="s">
+        <v>503</v>
+      </c>
+      <c r="I96" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>505</v>
+      </c>
+      <c r="B97" t="s">
+        <v>84</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" t="s">
+        <v>506</v>
+      </c>
+      <c r="E97" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" t="s">
+        <v>31</v>
+      </c>
+      <c r="G97" t="s">
+        <v>507</v>
+      </c>
+      <c r="H97" t="s">
+        <v>508</v>
+      </c>
+      <c r="I97" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>510</v>
+      </c>
+      <c r="B98" t="s">
+        <v>84</v>
+      </c>
+      <c r="C98" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" t="s">
+        <v>511</v>
+      </c>
+      <c r="E98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" t="s">
+        <v>512</v>
+      </c>
+      <c r="H98" t="s">
+        <v>513</v>
+      </c>
+      <c r="I98" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>515</v>
+      </c>
+      <c r="B99" t="s">
+        <v>36</v>
+      </c>
+      <c r="C99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" t="s">
+        <v>516</v>
+      </c>
+      <c r="E99" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99" t="s">
+        <v>517</v>
+      </c>
+      <c r="H99" t="s">
+        <v>518</v>
+      </c>
+      <c r="I99" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>520</v>
+      </c>
+      <c r="B100" t="s">
+        <v>36</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" t="s">
+        <v>521</v>
+      </c>
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100" t="s">
+        <v>522</v>
+      </c>
+      <c r="H100" t="s">
+        <v>523</v>
+      </c>
+      <c r="I100" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>525</v>
+      </c>
+      <c r="B101" t="s">
+        <v>36</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" t="s">
+        <v>526</v>
+      </c>
+      <c r="E101" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101" t="s">
+        <v>527</v>
+      </c>
+      <c r="H101" t="s">
+        <v>528</v>
+      </c>
+      <c r="I101" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>530</v>
+      </c>
+      <c r="B102" t="s">
+        <v>237</v>
+      </c>
+      <c r="C102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" t="s">
+        <v>531</v>
+      </c>
+      <c r="E102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" t="s">
+        <v>31</v>
+      </c>
+      <c r="G102" t="s">
+        <v>532</v>
+      </c>
+      <c r="H102" t="s">
+        <v>533</v>
+      </c>
+      <c r="I102" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>535</v>
+      </c>
+      <c r="B103" t="s">
+        <v>84</v>
+      </c>
+      <c r="C103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" t="s">
+        <v>536</v>
+      </c>
+      <c r="E103" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" t="s">
+        <v>31</v>
+      </c>
+      <c r="G103" t="s">
+        <v>537</v>
+      </c>
+      <c r="H103" t="s">
+        <v>538</v>
+      </c>
+      <c r="I103" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>540</v>
+      </c>
+      <c r="B104" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" t="s">
+        <v>541</v>
+      </c>
+      <c r="E104" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" t="s">
+        <v>31</v>
+      </c>
+      <c r="G104" t="s">
+        <v>542</v>
+      </c>
+      <c r="H104" t="s">
+        <v>543</v>
+      </c>
+      <c r="I104" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>545</v>
+      </c>
+      <c r="B105" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" t="s">
+        <v>546</v>
+      </c>
+      <c r="E105" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" t="s">
+        <v>31</v>
+      </c>
+      <c r="G105" t="s">
+        <v>547</v>
+      </c>
+      <c r="H105" t="s">
+        <v>548</v>
+      </c>
+      <c r="I105" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>550</v>
+      </c>
+      <c r="B106" t="s">
+        <v>36</v>
+      </c>
+      <c r="C106" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" t="s">
+        <v>551</v>
+      </c>
+      <c r="E106" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" t="s">
+        <v>31</v>
+      </c>
+      <c r="G106" t="s">
+        <v>552</v>
+      </c>
+      <c r="H106" t="s">
+        <v>553</v>
+      </c>
+      <c r="I106" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>555</v>
+      </c>
+      <c r="B107" t="s">
+        <v>36</v>
+      </c>
+      <c r="C107" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" t="s">
+        <v>556</v>
+      </c>
+      <c r="E107" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" t="s">
+        <v>31</v>
+      </c>
+      <c r="G107" t="s">
+        <v>557</v>
+      </c>
+      <c r="H107" t="s">
+        <v>558</v>
+      </c>
+      <c r="I107" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>560</v>
+      </c>
+      <c r="B108" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" t="s">
+        <v>561</v>
+      </c>
+      <c r="E108" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" t="s">
+        <v>31</v>
+      </c>
+      <c r="G108" t="s">
+        <v>562</v>
+      </c>
+      <c r="H108" t="s">
+        <v>563</v>
+      </c>
+      <c r="I108" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>565</v>
+      </c>
+      <c r="B109" t="s">
+        <v>103</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" t="s">
+        <v>566</v>
+      </c>
+      <c r="E109" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" t="s">
+        <v>98</v>
+      </c>
+      <c r="G109" t="s">
+        <v>567</v>
+      </c>
+      <c r="H109" t="s">
+        <v>568</v>
+      </c>
+      <c r="I109" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>570</v>
+      </c>
+      <c r="B110" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" t="s">
+        <v>571</v>
+      </c>
+      <c r="E110" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" t="s">
+        <v>31</v>
+      </c>
+      <c r="G110" t="s">
+        <v>572</v>
+      </c>
+      <c r="H110" t="s">
+        <v>573</v>
+      </c>
+      <c r="I110" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>575</v>
+      </c>
+      <c r="B111" t="s">
+        <v>36</v>
+      </c>
+      <c r="C111" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" t="s">
+        <v>576</v>
+      </c>
+      <c r="E111" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" t="s">
+        <v>31</v>
+      </c>
+      <c r="G111" t="s">
+        <v>577</v>
+      </c>
+      <c r="H111" t="s">
+        <v>578</v>
+      </c>
+      <c r="I111" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>580</v>
+      </c>
+      <c r="B112" t="s">
+        <v>36</v>
+      </c>
+      <c r="C112" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" t="s">
+        <v>581</v>
+      </c>
+      <c r="E112" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" t="s">
+        <v>31</v>
+      </c>
+      <c r="G112" t="s">
+        <v>582</v>
+      </c>
+      <c r="H112" t="s">
+        <v>583</v>
+      </c>
+      <c r="I112" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>585</v>
+      </c>
+      <c r="B113" t="s">
+        <v>36</v>
+      </c>
+      <c r="C113" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" t="s">
+        <v>586</v>
+      </c>
+      <c r="E113" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" t="s">
+        <v>98</v>
+      </c>
+      <c r="G113" t="s">
+        <v>587</v>
+      </c>
+      <c r="H113" t="s">
+        <v>588</v>
+      </c>
+      <c r="I113" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>590</v>
+      </c>
+      <c r="B114" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" t="s">
+        <v>591</v>
+      </c>
+      <c r="E114" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" t="s">
+        <v>31</v>
+      </c>
+      <c r="G114" t="s">
+        <v>592</v>
+      </c>
+      <c r="H114" t="s">
+        <v>593</v>
+      </c>
+      <c r="I114" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>595</v>
+      </c>
+      <c r="B115" t="s">
+        <v>36</v>
+      </c>
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" t="s">
+        <v>596</v>
+      </c>
+      <c r="E115" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G115" t="s">
+        <v>597</v>
+      </c>
+      <c r="H115" t="s">
+        <v>598</v>
+      </c>
+      <c r="I115" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>600</v>
+      </c>
+      <c r="B116" t="s">
+        <v>36</v>
+      </c>
+      <c r="C116" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116" t="s">
+        <v>601</v>
+      </c>
+      <c r="E116" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" t="s">
+        <v>98</v>
+      </c>
+      <c r="G116" t="s">
+        <v>602</v>
+      </c>
+      <c r="H116" t="s">
+        <v>603</v>
+      </c>
+      <c r="I116" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>605</v>
+      </c>
+      <c r="B117" t="s">
+        <v>36</v>
+      </c>
+      <c r="C117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" t="s">
+        <v>606</v>
+      </c>
+      <c r="E117" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" t="s">
+        <v>31</v>
+      </c>
+      <c r="G117" t="s">
+        <v>607</v>
+      </c>
+      <c r="H117" t="s">
+        <v>608</v>
+      </c>
+      <c r="I117" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>610</v>
+      </c>
+      <c r="B118" t="s">
+        <v>10</v>
+      </c>
+      <c r="C118" t="s">
+        <v>14</v>
+      </c>
+      <c r="D118" t="s">
+        <v>611</v>
+      </c>
+      <c r="E118" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" t="s">
+        <v>612</v>
+      </c>
+      <c r="H118" t="s">
+        <v>10</v>
+      </c>
+      <c r="I118" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>614</v>
+      </c>
+      <c r="B119" t="s">
+        <v>90</v>
+      </c>
+      <c r="C119" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119" t="s">
+        <v>615</v>
+      </c>
+      <c r="E119" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" t="s">
+        <v>31</v>
+      </c>
+      <c r="G119" t="s">
+        <v>616</v>
+      </c>
+      <c r="H119" t="s">
+        <v>93</v>
+      </c>
+      <c r="I119" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>618</v>
+      </c>
+      <c r="B120" t="s">
+        <v>36</v>
+      </c>
+      <c r="C120" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" t="s">
+        <v>619</v>
+      </c>
+      <c r="E120" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" t="s">
+        <v>31</v>
+      </c>
+      <c r="G120" t="s">
+        <v>620</v>
+      </c>
+      <c r="H120" t="s">
+        <v>621</v>
+      </c>
+      <c r="I120" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>623</v>
+      </c>
+      <c r="B121" t="s">
+        <v>624</v>
+      </c>
+      <c r="C121" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" t="s">
+        <v>625</v>
+      </c>
+      <c r="E121" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" t="s">
+        <v>626</v>
+      </c>
+      <c r="G121" t="s">
+        <v>627</v>
+      </c>
+      <c r="H121" t="s">
+        <v>628</v>
+      </c>
+      <c r="I121" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>630</v>
+      </c>
+      <c r="B122" t="s">
+        <v>96</v>
+      </c>
+      <c r="C122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" t="s">
+        <v>631</v>
+      </c>
+      <c r="E122" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" t="s">
+        <v>98</v>
+      </c>
+      <c r="G122" t="s">
+        <v>632</v>
+      </c>
+      <c r="H122" t="s">
+        <v>633</v>
+      </c>
+      <c r="I122" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>635</v>
+      </c>
+      <c r="B123" t="s">
+        <v>636</v>
+      </c>
+      <c r="C123" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" t="s">
+        <v>637</v>
+      </c>
+      <c r="E123" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" t="s">
+        <v>98</v>
+      </c>
+      <c r="G123" t="s">
+        <v>638</v>
+      </c>
+      <c r="H123" t="s">
+        <v>639</v>
+      </c>
+      <c r="I123" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>641</v>
+      </c>
+      <c r="B124" t="s">
+        <v>96</v>
+      </c>
+      <c r="C124" t="s">
+        <v>10</v>
+      </c>
+      <c r="D124" t="s">
+        <v>642</v>
+      </c>
+      <c r="E124" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" t="s">
+        <v>98</v>
+      </c>
+      <c r="G124" t="s">
+        <v>643</v>
+      </c>
+      <c r="H124" t="s">
+        <v>644</v>
+      </c>
+      <c r="I124" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>646</v>
+      </c>
+      <c r="B125" t="s">
+        <v>36</v>
+      </c>
+      <c r="C125" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" t="s">
+        <v>647</v>
+      </c>
+      <c r="E125" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" t="s">
+        <v>98</v>
+      </c>
+      <c r="G125" t="s">
+        <v>648</v>
+      </c>
+      <c r="H125" t="s">
+        <v>649</v>
+      </c>
+      <c r="I125" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>651</v>
+      </c>
+      <c r="B126" t="s">
+        <v>36</v>
+      </c>
+      <c r="C126" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" t="s">
+        <v>652</v>
+      </c>
+      <c r="E126" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" t="s">
+        <v>31</v>
+      </c>
+      <c r="G126" t="s">
+        <v>653</v>
+      </c>
+      <c r="H126" t="s">
+        <v>654</v>
+      </c>
+      <c r="I126" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>656</v>
+      </c>
+      <c r="B127" t="s">
+        <v>36</v>
+      </c>
+      <c r="C127" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" t="s">
+        <v>657</v>
+      </c>
+      <c r="E127" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" t="s">
+        <v>31</v>
+      </c>
+      <c r="G127" t="s">
+        <v>658</v>
+      </c>
+      <c r="H127" t="s">
+        <v>659</v>
+      </c>
+      <c r="I127" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>661</v>
+      </c>
+      <c r="B128" t="s">
+        <v>237</v>
+      </c>
+      <c r="C128" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" t="s">
+        <v>662</v>
+      </c>
+      <c r="E128" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" t="s">
+        <v>31</v>
+      </c>
+      <c r="G128" t="s">
+        <v>663</v>
+      </c>
+      <c r="H128" t="s">
+        <v>664</v>
+      </c>
+      <c r="I128" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>666</v>
+      </c>
+      <c r="B129" t="s">
+        <v>36</v>
+      </c>
+      <c r="C129" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" t="s">
+        <v>667</v>
+      </c>
+      <c r="E129" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" t="s">
+        <v>98</v>
+      </c>
+      <c r="G129" t="s">
+        <v>668</v>
+      </c>
+      <c r="H129" t="s">
+        <v>669</v>
+      </c>
+      <c r="I129" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>671</v>
+      </c>
+      <c r="B130" t="s">
+        <v>96</v>
+      </c>
+      <c r="C130" t="s">
+        <v>10</v>
+      </c>
+      <c r="D130" t="s">
+        <v>672</v>
+      </c>
+      <c r="E130" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" t="s">
+        <v>98</v>
+      </c>
+      <c r="G130" t="s">
+        <v>673</v>
+      </c>
+      <c r="H130" t="s">
+        <v>674</v>
+      </c>
+      <c r="I130" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>676</v>
+      </c>
+      <c r="B131" t="s">
+        <v>36</v>
+      </c>
+      <c r="C131" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131" t="s">
+        <v>677</v>
+      </c>
+      <c r="E131" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" t="s">
+        <v>98</v>
+      </c>
+      <c r="G131" t="s">
+        <v>678</v>
+      </c>
+      <c r="H131" t="s">
+        <v>679</v>
+      </c>
+      <c r="I131" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>681</v>
+      </c>
+      <c r="B132" t="s">
+        <v>682</v>
+      </c>
+      <c r="C132" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" t="s">
+        <v>683</v>
+      </c>
+      <c r="E132" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" t="s">
+        <v>684</v>
+      </c>
+      <c r="G132" t="s">
+        <v>685</v>
+      </c>
+      <c r="H132" t="s">
+        <v>686</v>
+      </c>
+      <c r="I132" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>688</v>
+      </c>
+      <c r="B133" t="s">
+        <v>36</v>
+      </c>
+      <c r="C133" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" t="s">
+        <v>689</v>
+      </c>
+      <c r="E133" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" t="s">
+        <v>31</v>
+      </c>
+      <c r="G133" t="s">
+        <v>690</v>
+      </c>
+      <c r="H133" t="s">
+        <v>691</v>
+      </c>
+      <c r="I133" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>693</v>
+      </c>
+      <c r="B134" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" t="s">
-        <v>71</v>
+      <c r="D134" t="s">
+        <v>694</v>
+      </c>
+      <c r="E134" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
+        <v>695</v>
+      </c>
+      <c r="H134" t="s">
+        <v>10</v>
+      </c>
+      <c r="I134" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>697</v>
+      </c>
+      <c r="B135" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" t="s">
+        <v>698</v>
+      </c>
+      <c r="E135" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" t="s">
+        <v>20</v>
+      </c>
+      <c r="G135" t="s">
+        <v>699</v>
+      </c>
+      <c r="H135" t="s">
+        <v>461</v>
+      </c>
+      <c r="I135" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>701</v>
+      </c>
+      <c r="B136" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" t="s">
+        <v>14</v>
+      </c>
+      <c r="D136" t="s">
+        <v>702</v>
+      </c>
+      <c r="E136" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" t="s">
+        <v>14</v>
+      </c>
+      <c r="G136" t="s">
+        <v>703</v>
+      </c>
+      <c r="H136" t="s">
+        <v>10</v>
+      </c>
+      <c r="I136" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>705</v>
+      </c>
+      <c r="B137" t="s">
+        <v>706</v>
+      </c>
+      <c r="C137" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" t="s">
+        <v>707</v>
+      </c>
+      <c r="E137" t="s">
+        <v>13</v>
+      </c>
+      <c r="F137" t="s">
+        <v>708</v>
+      </c>
+      <c r="G137" t="s">
+        <v>709</v>
+      </c>
+      <c r="H137" t="s">
+        <v>710</v>
+      </c>
+      <c r="I137" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>712</v>
+      </c>
+      <c r="B138" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" t="s">
+        <v>713</v>
+      </c>
+      <c r="D138" t="s">
+        <v>714</v>
+      </c>
+      <c r="E138" t="s">
+        <v>13</v>
+      </c>
+      <c r="F138" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138" t="s">
+        <v>715</v>
+      </c>
+      <c r="H138" t="s">
+        <v>10</v>
+      </c>
+      <c r="I138" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>717</v>
+      </c>
+      <c r="B139" t="s">
+        <v>718</v>
+      </c>
+      <c r="C139" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139" t="s">
+        <v>719</v>
+      </c>
+      <c r="E139" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139" t="s">
+        <v>116</v>
+      </c>
+      <c r="G139" t="s">
+        <v>720</v>
+      </c>
+      <c r="H139" t="s">
+        <v>721</v>
+      </c>
+      <c r="I139" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>723</v>
+      </c>
+      <c r="B140" t="s">
+        <v>84</v>
+      </c>
+      <c r="C140" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" t="s">
+        <v>724</v>
+      </c>
+      <c r="E140" t="s">
+        <v>13</v>
+      </c>
+      <c r="F140" t="s">
+        <v>31</v>
+      </c>
+      <c r="G140" t="s">
+        <v>725</v>
+      </c>
+      <c r="H140" t="s">
+        <v>726</v>
+      </c>
+      <c r="I140" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>728</v>
+      </c>
+      <c r="B141" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" t="s">
+        <v>713</v>
+      </c>
+      <c r="D141" t="s">
+        <v>729</v>
+      </c>
+      <c r="E141" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s">
+        <v>730</v>
+      </c>
+      <c r="H141" t="s">
+        <v>10</v>
+      </c>
+      <c r="I141" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>732</v>
+      </c>
+      <c r="B142" t="s">
+        <v>36</v>
+      </c>
+      <c r="C142" t="s">
+        <v>10</v>
+      </c>
+      <c r="D142" t="s">
+        <v>733</v>
+      </c>
+      <c r="E142" t="s">
+        <v>13</v>
+      </c>
+      <c r="F142" t="s">
+        <v>31</v>
+      </c>
+      <c r="G142" t="s">
+        <v>734</v>
+      </c>
+      <c r="H142" t="s">
+        <v>659</v>
+      </c>
+      <c r="I142" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>736</v>
+      </c>
+      <c r="B143" t="s">
+        <v>36</v>
+      </c>
+      <c r="C143" t="s">
+        <v>10</v>
+      </c>
+      <c r="D143" t="s">
+        <v>737</v>
+      </c>
+      <c r="E143" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" t="s">
+        <v>31</v>
+      </c>
+      <c r="G143" t="s">
+        <v>738</v>
+      </c>
+      <c r="H143" t="s">
+        <v>739</v>
+      </c>
+      <c r="I143" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>741</v>
+      </c>
+      <c r="B144" t="s">
+        <v>84</v>
+      </c>
+      <c r="C144" t="s">
+        <v>10</v>
+      </c>
+      <c r="D144" t="s">
+        <v>742</v>
+      </c>
+      <c r="E144" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144" t="s">
+        <v>31</v>
+      </c>
+      <c r="G144" t="s">
+        <v>743</v>
+      </c>
+      <c r="H144" t="s">
+        <v>744</v>
+      </c>
+      <c r="I144" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>746</v>
+      </c>
+      <c r="B145" t="s">
+        <v>84</v>
+      </c>
+      <c r="C145" t="s">
+        <v>10</v>
+      </c>
+      <c r="D145" t="s">
+        <v>747</v>
+      </c>
+      <c r="E145" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145" t="s">
+        <v>31</v>
+      </c>
+      <c r="G145" t="s">
+        <v>748</v>
+      </c>
+      <c r="H145" t="s">
+        <v>749</v>
+      </c>
+      <c r="I145" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>751</v>
+      </c>
+      <c r="B146" t="s">
+        <v>718</v>
+      </c>
+      <c r="C146" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146" t="s">
+        <v>752</v>
+      </c>
+      <c r="E146" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146" t="s">
+        <v>116</v>
+      </c>
+      <c r="G146" t="s">
+        <v>753</v>
+      </c>
+      <c r="H146" t="s">
+        <v>721</v>
+      </c>
+      <c r="I146" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>755</v>
+      </c>
+      <c r="B147" t="s">
+        <v>36</v>
+      </c>
+      <c r="C147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D147" t="s">
+        <v>756</v>
+      </c>
+      <c r="E147" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" t="s">
+        <v>31</v>
+      </c>
+      <c r="G147" t="s">
+        <v>757</v>
+      </c>
+      <c r="H147" t="s">
+        <v>758</v>
+      </c>
+      <c r="I147" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>760</v>
+      </c>
+      <c r="B148" t="s">
+        <v>84</v>
+      </c>
+      <c r="C148" t="s">
+        <v>10</v>
+      </c>
+      <c r="D148" t="s">
+        <v>761</v>
+      </c>
+      <c r="E148" t="s">
+        <v>13</v>
+      </c>
+      <c r="F148" t="s">
+        <v>31</v>
+      </c>
+      <c r="G148" t="s">
+        <v>762</v>
+      </c>
+      <c r="H148" t="s">
+        <v>726</v>
+      </c>
+      <c r="I148" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>764</v>
+      </c>
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" t="s">
+        <v>713</v>
+      </c>
+      <c r="D149" t="s">
+        <v>765</v>
+      </c>
+      <c r="E149" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" t="s">
+        <v>766</v>
+      </c>
+      <c r="H149" t="s">
+        <v>10</v>
+      </c>
+      <c r="I149" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>768</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" t="s">
+        <v>713</v>
+      </c>
+      <c r="D150" t="s">
+        <v>769</v>
+      </c>
+      <c r="E150" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" t="s">
+        <v>770</v>
+      </c>
+      <c r="H150" t="s">
+        <v>10</v>
+      </c>
+      <c r="I150" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>772</v>
+      </c>
+      <c r="B151" t="s">
+        <v>773</v>
+      </c>
+      <c r="C151" t="s">
+        <v>10</v>
+      </c>
+      <c r="D151" t="s">
+        <v>774</v>
+      </c>
+      <c r="E151" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" t="s">
+        <v>775</v>
+      </c>
+      <c r="G151" t="s">
+        <v>776</v>
+      </c>
+      <c r="H151" t="s">
+        <v>777</v>
+      </c>
+      <c r="I151" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>779</v>
+      </c>
+      <c r="B152" t="s">
+        <v>780</v>
+      </c>
+      <c r="C152" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" t="s">
+        <v>781</v>
+      </c>
+      <c r="E152" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" t="s">
+        <v>116</v>
+      </c>
+      <c r="G152" t="s">
+        <v>782</v>
+      </c>
+      <c r="H152" t="s">
+        <v>783</v>
+      </c>
+      <c r="I152" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>785</v>
+      </c>
+      <c r="B153" t="s">
+        <v>780</v>
+      </c>
+      <c r="C153" t="s">
+        <v>10</v>
+      </c>
+      <c r="D153" t="s">
+        <v>786</v>
+      </c>
+      <c r="E153" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" t="s">
+        <v>116</v>
+      </c>
+      <c r="G153" t="s">
+        <v>787</v>
+      </c>
+      <c r="H153" t="s">
+        <v>788</v>
+      </c>
+      <c r="I153" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>790</v>
+      </c>
+      <c r="B154" t="s">
+        <v>791</v>
+      </c>
+      <c r="C154" t="s">
+        <v>10</v>
+      </c>
+      <c r="D154" t="s">
+        <v>792</v>
+      </c>
+      <c r="E154" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" t="s">
+        <v>793</v>
+      </c>
+      <c r="G154" t="s">
+        <v>794</v>
+      </c>
+      <c r="H154" t="s">
+        <v>10</v>
+      </c>
+      <c r="I154" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>796</v>
+      </c>
+      <c r="B155" t="s">
+        <v>36</v>
+      </c>
+      <c r="C155" t="s">
+        <v>10</v>
+      </c>
+      <c r="D155" t="s">
+        <v>797</v>
+      </c>
+      <c r="E155" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" t="s">
+        <v>31</v>
+      </c>
+      <c r="G155" t="s">
+        <v>798</v>
+      </c>
+      <c r="H155" t="s">
+        <v>799</v>
+      </c>
+      <c r="I155" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>801</v>
+      </c>
+      <c r="B156" t="s">
+        <v>90</v>
+      </c>
+      <c r="C156" t="s">
+        <v>10</v>
+      </c>
+      <c r="D156" t="s">
+        <v>802</v>
+      </c>
+      <c r="E156" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" t="s">
+        <v>31</v>
+      </c>
+      <c r="G156" t="s">
+        <v>803</v>
+      </c>
+      <c r="H156" t="s">
+        <v>804</v>
+      </c>
+      <c r="I156" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>806</v>
+      </c>
+      <c r="B157" t="s">
+        <v>36</v>
+      </c>
+      <c r="C157" t="s">
+        <v>10</v>
+      </c>
+      <c r="D157" t="s">
+        <v>807</v>
+      </c>
+      <c r="E157" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" t="s">
+        <v>31</v>
+      </c>
+      <c r="G157" t="s">
+        <v>808</v>
+      </c>
+      <c r="H157" t="s">
+        <v>809</v>
+      </c>
+      <c r="I157" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>811</v>
+      </c>
+      <c r="B158" t="s">
+        <v>36</v>
+      </c>
+      <c r="C158" t="s">
+        <v>10</v>
+      </c>
+      <c r="D158" t="s">
+        <v>812</v>
+      </c>
+      <c r="E158" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" t="s">
+        <v>31</v>
+      </c>
+      <c r="G158" t="s">
+        <v>813</v>
+      </c>
+      <c r="H158" t="s">
+        <v>814</v>
+      </c>
+      <c r="I158" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>816</v>
+      </c>
+      <c r="B159" t="s">
+        <v>84</v>
+      </c>
+      <c r="C159" t="s">
+        <v>10</v>
+      </c>
+      <c r="D159" t="s">
+        <v>817</v>
+      </c>
+      <c r="E159" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" t="s">
+        <v>31</v>
+      </c>
+      <c r="G159" t="s">
+        <v>818</v>
+      </c>
+      <c r="H159" t="s">
+        <v>819</v>
+      </c>
+      <c r="I159" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>821</v>
+      </c>
+      <c r="B160" t="s">
+        <v>822</v>
+      </c>
+      <c r="C160" t="s">
+        <v>10</v>
+      </c>
+      <c r="D160" t="s">
+        <v>823</v>
+      </c>
+      <c r="E160" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" t="s">
+        <v>31</v>
+      </c>
+      <c r="G160" t="s">
+        <v>824</v>
+      </c>
+      <c r="H160" t="s">
+        <v>825</v>
+      </c>
+      <c r="I160" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>827</v>
+      </c>
+      <c r="B161" t="s">
+        <v>84</v>
+      </c>
+      <c r="C161" t="s">
+        <v>10</v>
+      </c>
+      <c r="D161" t="s">
+        <v>828</v>
+      </c>
+      <c r="E161" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" t="s">
+        <v>31</v>
+      </c>
+      <c r="G161" t="s">
+        <v>829</v>
+      </c>
+      <c r="H161" t="s">
+        <v>830</v>
+      </c>
+      <c r="I161" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>832</v>
+      </c>
+      <c r="B162" t="s">
+        <v>84</v>
+      </c>
+      <c r="C162" t="s">
+        <v>10</v>
+      </c>
+      <c r="D162" t="s">
+        <v>833</v>
+      </c>
+      <c r="E162" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" t="s">
+        <v>31</v>
+      </c>
+      <c r="G162" t="s">
+        <v>834</v>
+      </c>
+      <c r="H162" t="s">
+        <v>835</v>
+      </c>
+      <c r="I162" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>837</v>
+      </c>
+      <c r="B163" t="s">
+        <v>36</v>
+      </c>
+      <c r="C163" t="s">
+        <v>10</v>
+      </c>
+      <c r="D163" t="s">
+        <v>838</v>
+      </c>
+      <c r="E163" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" t="s">
+        <v>31</v>
+      </c>
+      <c r="G163" t="s">
+        <v>839</v>
+      </c>
+      <c r="H163" t="s">
+        <v>840</v>
+      </c>
+      <c r="I163" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>842</v>
+      </c>
+      <c r="B164" t="s">
+        <v>36</v>
+      </c>
+      <c r="C164" t="s">
+        <v>10</v>
+      </c>
+      <c r="D164" t="s">
+        <v>843</v>
+      </c>
+      <c r="E164" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" t="s">
+        <v>31</v>
+      </c>
+      <c r="G164" t="s">
+        <v>844</v>
+      </c>
+      <c r="H164" t="s">
+        <v>845</v>
+      </c>
+      <c r="I164" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>847</v>
+      </c>
+      <c r="B165" t="s">
+        <v>84</v>
+      </c>
+      <c r="C165" t="s">
+        <v>10</v>
+      </c>
+      <c r="D165" t="s">
+        <v>848</v>
+      </c>
+      <c r="E165" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165" t="s">
+        <v>31</v>
+      </c>
+      <c r="G165" t="s">
+        <v>849</v>
+      </c>
+      <c r="H165" t="s">
+        <v>850</v>
+      </c>
+      <c r="I165" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>852</v>
+      </c>
+      <c r="B166" t="s">
+        <v>237</v>
+      </c>
+      <c r="C166" t="s">
+        <v>10</v>
+      </c>
+      <c r="D166" t="s">
+        <v>853</v>
+      </c>
+      <c r="E166" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" t="s">
+        <v>31</v>
+      </c>
+      <c r="G166" t="s">
+        <v>854</v>
+      </c>
+      <c r="H166" t="s">
+        <v>855</v>
+      </c>
+      <c r="I166" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>857</v>
+      </c>
+      <c r="B167" t="s">
+        <v>195</v>
+      </c>
+      <c r="C167" t="s">
+        <v>10</v>
+      </c>
+      <c r="D167" t="s">
+        <v>858</v>
+      </c>
+      <c r="E167" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" t="s">
+        <v>31</v>
+      </c>
+      <c r="G167" t="s">
+        <v>859</v>
+      </c>
+      <c r="H167" t="s">
+        <v>860</v>
+      </c>
+      <c r="I167" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>862</v>
+      </c>
+      <c r="B168" t="s">
+        <v>36</v>
+      </c>
+      <c r="C168" t="s">
+        <v>10</v>
+      </c>
+      <c r="D168" t="s">
+        <v>863</v>
+      </c>
+      <c r="E168" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" t="s">
+        <v>31</v>
+      </c>
+      <c r="G168" t="s">
+        <v>864</v>
+      </c>
+      <c r="H168" t="s">
+        <v>865</v>
+      </c>
+      <c r="I168" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>867</v>
+      </c>
+      <c r="B169" t="s">
+        <v>84</v>
+      </c>
+      <c r="C169" t="s">
+        <v>10</v>
+      </c>
+      <c r="D169" t="s">
+        <v>868</v>
+      </c>
+      <c r="E169" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" t="s">
+        <v>31</v>
+      </c>
+      <c r="G169" t="s">
+        <v>869</v>
+      </c>
+      <c r="H169" t="s">
+        <v>870</v>
+      </c>
+      <c r="I169" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>872</v>
+      </c>
+      <c r="B170" t="s">
+        <v>36</v>
+      </c>
+      <c r="C170" t="s">
+        <v>10</v>
+      </c>
+      <c r="D170" t="s">
+        <v>873</v>
+      </c>
+      <c r="E170" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" t="s">
+        <v>31</v>
+      </c>
+      <c r="G170" t="s">
+        <v>874</v>
+      </c>
+      <c r="H170" t="s">
+        <v>875</v>
+      </c>
+      <c r="I170" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>877</v>
+      </c>
+      <c r="B171" t="s">
+        <v>84</v>
+      </c>
+      <c r="C171" t="s">
+        <v>10</v>
+      </c>
+      <c r="D171" t="s">
+        <v>878</v>
+      </c>
+      <c r="E171" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" t="s">
+        <v>31</v>
+      </c>
+      <c r="G171" t="s">
+        <v>879</v>
+      </c>
+      <c r="H171" t="s">
+        <v>880</v>
+      </c>
+      <c r="I171" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>882</v>
+      </c>
+      <c r="B172" t="s">
+        <v>883</v>
+      </c>
+      <c r="C172" t="s">
+        <v>10</v>
+      </c>
+      <c r="D172" t="s">
+        <v>884</v>
+      </c>
+      <c r="E172" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" t="s">
+        <v>31</v>
+      </c>
+      <c r="G172" t="s">
+        <v>885</v>
+      </c>
+      <c r="H172" t="s">
+        <v>886</v>
+      </c>
+      <c r="I172" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>888</v>
+      </c>
+      <c r="B173" t="s">
+        <v>84</v>
+      </c>
+      <c r="C173" t="s">
+        <v>10</v>
+      </c>
+      <c r="D173" t="s">
+        <v>889</v>
+      </c>
+      <c r="E173" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" t="s">
+        <v>31</v>
+      </c>
+      <c r="G173" t="s">
+        <v>890</v>
+      </c>
+      <c r="H173" t="s">
+        <v>891</v>
+      </c>
+      <c r="I173" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>893</v>
+      </c>
+      <c r="B174" t="s">
+        <v>894</v>
+      </c>
+      <c r="C174" t="s">
+        <v>10</v>
+      </c>
+      <c r="D174" t="s">
+        <v>895</v>
+      </c>
+      <c r="E174" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" t="s">
+        <v>775</v>
+      </c>
+      <c r="G174" t="s">
+        <v>896</v>
+      </c>
+      <c r="H174" t="s">
+        <v>897</v>
+      </c>
+      <c r="I174" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>899</v>
+      </c>
+      <c r="B175" t="s">
+        <v>900</v>
+      </c>
+      <c r="C175" t="s">
+        <v>10</v>
+      </c>
+      <c r="D175" t="s">
+        <v>901</v>
+      </c>
+      <c r="E175" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" t="s">
+        <v>902</v>
+      </c>
+      <c r="G175" t="s">
+        <v>903</v>
+      </c>
+      <c r="H175" t="s">
+        <v>904</v>
+      </c>
+      <c r="I175" t="s">
+        <v>905</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-app-entry.report.xlsx
+++ b/tools/importer/reports/import-app-entry.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="997">
   <si>
     <t>_reportFile</t>
   </si>
@@ -76,7 +76,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-10-21T22:28:43.065Z</t>
+    <t>2026-10-22T00:04:34.822Z</t>
   </si>
   <si>
     <t>Jetzt Flug buchen – mit Lufthansa zu über 200 Zielen reisen | Lufthansa</t>
@@ -109,7 +109,7 @@
     <t>info</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:06.345Z</t>
+    <t>2026-10-22T00:06:56.327Z</t>
   </si>
   <si>
     <t>Doctor on Board – Gut zu wissen | Lufthansa</t>
@@ -127,7 +127,7 @@
     <t>de/de/doctor-on-board</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:01.082Z</t>
+    <t>2026-10-22T00:06:53.771Z</t>
   </si>
   <si>
     <t>Doctor on Board | Lufthansa</t>
@@ -154,7 +154,7 @@
     <t>de/de/homepage</t>
   </si>
   <si>
-    <t>2026-10-21T22:28:39.550Z</t>
+    <t>2026-10-22T00:04:31.566Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/de/homepage</t>
@@ -166,7 +166,7 @@
     <t>de/de/kinder-an-bord</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:25.780Z</t>
+    <t>2026-10-22T00:06:25.540Z</t>
   </si>
   <si>
     <t>Mit Kindern und Babys an Bord | Lufthansa</t>
@@ -181,7 +181,7 @@
     <t>de/de/kindermenues-an-bord</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:30.745Z</t>
+    <t>2026-10-22T00:06:27.437Z</t>
   </si>
   <si>
     <t>Kindermenüs | Lufthansa</t>
@@ -196,7 +196,7 @@
     <t>de/de/lufthansa-first-class-entertainment</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:02.541Z</t>
+    <t>2026-10-22T00:07:04.250Z</t>
   </si>
   <si>
     <t>Entertainment Welt | Lufthansa</t>
@@ -211,7 +211,7 @@
     <t>de/de/lufthansa-first-class-komfort</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:46.333Z</t>
+    <t>2026-10-22T00:07:01.009Z</t>
   </si>
   <si>
     <t>Komfort an Bord der First Class | Lufthansa</t>
@@ -226,7 +226,7 @@
     <t>de/de/menues-auf-langstreckenfluegen</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:20.948Z</t>
+    <t>2026-10-22T00:06:31.893Z</t>
   </si>
   <si>
     <t>Menüs auf Langstreckenflügen | Lufthansa</t>
@@ -241,7 +241,7 @@
     <t>de/de/menues-reiseklassen</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:25.475Z</t>
+    <t>2026-10-22T00:06:33.541Z</t>
   </si>
   <si>
     <t>Menüs in unseren Reiseklassen | Lufthansa</t>
@@ -271,7 +271,7 @@
     <t>de/de/onboard-delights-faq</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:11.489Z</t>
+    <t>2026-10-22T00:06:29.767Z</t>
   </si>
   <si>
     <t>faq | Lufthansa</t>
@@ -289,7 +289,7 @@
     <t>de/de/onboard-delights</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:32.444Z</t>
+    <t>2026-10-22T00:06:36.967Z</t>
   </si>
   <si>
     <t>Onboard Delights | Lufthansa</t>
@@ -310,7 +310,7 @@
     <t>hub</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:36.688Z</t>
+    <t>2026-10-22T00:05:29.823Z</t>
   </si>
   <si>
     <t>Services an Bord | Lufthansa</t>
@@ -328,7 +328,7 @@
     <t>de/de/speisen-und-getraenke</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:10.255Z</t>
+    <t>2026-10-22T00:05:27.487Z</t>
   </si>
   <si>
     <t>Menüs an Bord | Lufthansa</t>
@@ -343,7 +343,7 @@
     <t>de/de/unterhaltung-an-bord</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:47.115Z</t>
+    <t>2026-10-22T00:07:07.052Z</t>
   </si>
   <si>
     <t>Unterhaltung an Bord | Lufthansa</t>
@@ -364,7 +364,7 @@
     <t>campaign</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:52.969Z</t>
+    <t>2026-10-22T00:11:17.425Z</t>
   </si>
   <si>
     <t>100 Years Lufthansa | Lufthansa</t>
@@ -385,7 +385,7 @@
     <t>fleet</t>
   </si>
   <si>
-    <t>2026-10-21T22:35:08.686Z</t>
+    <t>2026-10-22T00:11:32.785Z</t>
   </si>
   <si>
     <t>Airbus A350-900 | Lufthansa</t>
@@ -403,7 +403,7 @@
     <t>de/en/accessible-travel</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:47.559Z</t>
+    <t>2026-10-22T00:05:37.844Z</t>
   </si>
   <si>
     <t>Accessible travel | Lufthansa</t>
@@ -418,7 +418,7 @@
     <t>de/en/add-sports-baggage</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:49.905Z</t>
+    <t>2026-10-22T00:05:40.380Z</t>
   </si>
   <si>
     <t>Add sports baggage | Lufthansa</t>
@@ -433,7 +433,7 @@
     <t>de/en/additional-services</t>
   </si>
   <si>
-    <t>2026-10-21T22:28:54.578Z</t>
+    <t>2026-10-22T00:04:47.645Z</t>
   </si>
   <si>
     <t>Extra services | Lufthansa</t>
@@ -448,7 +448,7 @@
     <t>de/en/addresses-worldwide</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:51.608Z</t>
+    <t>2026-10-22T00:05:43.480Z</t>
   </si>
   <si>
     <t>Addresses worldwide | Lufthansa</t>
@@ -463,7 +463,7 @@
     <t>de/en/admission-rules</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:53.742Z</t>
+    <t>2026-10-22T00:05:46.370Z</t>
   </si>
   <si>
     <t>Access to our lounges | Lufthansa</t>
@@ -478,7 +478,7 @@
     <t>de/en/advance-seat-reservation</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:57.170Z</t>
+    <t>2026-10-22T00:05:48.515Z</t>
   </si>
   <si>
     <t>Advance seat reservation | Lufthansa</t>
@@ -496,7 +496,7 @@
     <t>de/en/advice-for-travellers-with-special-needs-to-and-from-the-usa</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:59.570Z</t>
+    <t>2026-10-22T00:05:50.516Z</t>
   </si>
   <si>
     <t>Information about accessible travel to the USA | Lufthansa</t>
@@ -511,7 +511,7 @@
     <t>de/en/affiliatemarketing</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:02.705Z</t>
+    <t>2026-10-22T00:05:53.108Z</t>
   </si>
   <si>
     <t>Affiliate marketing | Lufthansa</t>
@@ -526,7 +526,7 @@
     <t>de/en/airport-information</t>
   </si>
   <si>
-    <t>2026-10-21T22:28:57.157Z</t>
+    <t>2026-10-22T00:04:50.211Z</t>
   </si>
   <si>
     <t>Airport information | Lufthansa</t>
@@ -541,7 +541,7 @@
     <t>de/en/all-check-in</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:05.727Z</t>
+    <t>2026-10-22T00:05:55.473Z</t>
   </si>
   <si>
     <t>All check-in options | Lufthansa</t>
@@ -556,7 +556,7 @@
     <t>de/en/arrival-services</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:08.819Z</t>
+    <t>2026-10-22T00:05:58.520Z</t>
   </si>
   <si>
     <t>Arrival services | Lufthansa</t>
@@ -571,7 +571,7 @@
     <t>de/en/assistenzhunde</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:11.883Z</t>
+    <t>2026-10-22T00:06:00.885Z</t>
   </si>
   <si>
     <t>Assistance dogs | Lufthansa</t>
@@ -586,7 +586,7 @@
     <t>de/en/automatic-check-in</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:14.648Z</t>
+    <t>2026-10-22T00:06:03.899Z</t>
   </si>
   <si>
     <t>Automated check-in | Lufthansa</t>
@@ -604,7 +604,7 @@
     <t>de/en/baggage-irregularities</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:16.983Z</t>
+    <t>2026-10-22T00:06:06.833Z</t>
   </si>
   <si>
     <t>Problems with baggage | Lufthansa</t>
@@ -622,7 +622,7 @@
     <t>de/en/baggage</t>
   </si>
   <si>
-    <t>2026-10-21T22:28:51.748Z</t>
+    <t>2026-10-22T00:04:44.726Z</t>
   </si>
   <si>
     <t>Baggage | Lufthansa</t>
@@ -637,7 +637,7 @@
     <t>de/en/bid-upgrade</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:19.821Z</t>
+    <t>2026-10-22T00:06:08.945Z</t>
   </si>
   <si>
     <t>Submit an offer for your upgrade | Lufthansa</t>
@@ -652,7 +652,7 @@
     <t>de/en/boarding</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:22.222Z</t>
+    <t>2026-10-22T00:07:10.047Z</t>
   </si>
   <si>
     <t>Boarding | Lufthansa</t>
@@ -667,7 +667,7 @@
     <t>de/en/business-class-on-short-and-medium-haul</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:03.113Z</t>
+    <t>2026-10-22T00:08:25.247Z</t>
   </si>
   <si>
     <t>Business Class on short and medium-haul routes | Lufthansa</t>
@@ -682,7 +682,7 @@
     <t>de/en/business-class</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:00.658Z</t>
+    <t>2026-10-22T00:08:22.636Z</t>
   </si>
   <si>
     <t>Business Class | Lufthansa</t>
@@ -697,7 +697,7 @@
     <t>de/en/business-services</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:05.036Z</t>
+    <t>2026-10-22T00:08:27.393Z</t>
   </si>
   <si>
     <t>Business Services | Lufthansa</t>
@@ -712,7 +712,7 @@
     <t>de/en/cancellations-and-refunds</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:08.458Z</t>
+    <t>2026-10-22T00:08:30.459Z</t>
   </si>
   <si>
     <t>Cancellation and refund | Lufthansa</t>
@@ -730,7 +730,7 @@
     <t>de/en/carry-on-baggage</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:10.950Z</t>
+    <t>2026-10-22T00:08:32.966Z</t>
   </si>
   <si>
     <t>Carry-on baggage | Lufthansa</t>
@@ -745,7 +745,7 @@
     <t>de/en/cash-and-miles</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:14.017Z</t>
+    <t>2026-10-22T00:08:35.317Z</t>
   </si>
   <si>
     <t>Cash &amp; Miles | Lufthansa</t>
@@ -760,7 +760,7 @@
     <t>de/en/check-in-baggage</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:16.993Z</t>
+    <t>2026-10-22T00:08:38.784Z</t>
   </si>
   <si>
     <t>Baggage drop | Lufthansa</t>
@@ -775,7 +775,7 @@
     <t>de/en/check-in-with-the-family</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:18.810Z</t>
+    <t>2026-10-22T00:08:40.474Z</t>
   </si>
   <si>
     <t>Online check-in with the whole family | Lufthansa</t>
@@ -790,7 +790,7 @@
     <t>de/en/child-restraint-systems</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:20.992Z</t>
+    <t>2026-10-22T00:08:42.307Z</t>
   </si>
   <si>
     <t>Safety for small children on board | Lufthansa</t>
@@ -805,7 +805,7 @@
     <t>de/en/children-on-board</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:23.009Z</t>
+    <t>2026-10-22T00:06:11.558Z</t>
   </si>
   <si>
     <t>On board with children and babies | Lufthansa</t>
@@ -820,7 +820,7 @@
     <t>de/en/childrens-menus-on-board</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:28.164Z</t>
+    <t>2026-10-22T00:06:13.494Z</t>
   </si>
   <si>
     <t>Children’s menus | Lufthansa</t>
@@ -835,7 +835,7 @@
     <t>de/en/dangerous-dogs</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:34.059Z</t>
+    <t>2026-10-22T00:08:44.392Z</t>
   </si>
   <si>
     <t>Fighting dog breeds and snub-nosed animals | Lufthansa</t>
@@ -850,7 +850,7 @@
     <t>de/en/digital-baggage-services</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:36.282Z</t>
+    <t>2026-10-22T00:08:46.453Z</t>
   </si>
   <si>
     <t>Digital baggage services | Lufthansa</t>
@@ -865,7 +865,7 @@
     <t>de/en/digital-self-services</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:00.047Z</t>
+    <t>2026-10-22T00:04:53.064Z</t>
   </si>
   <si>
     <t>Digital services | Lufthansa</t>
@@ -880,7 +880,7 @@
     <t>de/en/digital-travel-companion</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:39.166Z</t>
+    <t>2026-10-22T00:08:49.146Z</t>
   </si>
   <si>
     <t>Lufthansa app | Lufthansa</t>
@@ -895,7 +895,7 @@
     <t>de/en/doctor-on-board-news</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:03.500Z</t>
+    <t>2026-10-22T00:06:40.774Z</t>
   </si>
   <si>
     <t>Doctor on Board—good to know | Lufthansa</t>
@@ -910,7 +910,7 @@
     <t>de/en/doctor-on-board</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:58.785Z</t>
+    <t>2026-10-22T00:06:38.649Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/doctor-on-board</t>
@@ -922,7 +922,7 @@
     <t>de/en/economy-class</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:21.285Z</t>
+    <t>2026-10-22T00:09:11.033Z</t>
   </si>
   <si>
     <t>Economy Class | Lufthansa</t>
@@ -937,7 +937,7 @@
     <t>de/en/electronic-bag-tags</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:23.940Z</t>
+    <t>2026-10-22T00:09:12.902Z</t>
   </si>
   <si>
     <t>Electronic bag tags | Lufthansa</t>
@@ -952,7 +952,7 @@
     <t>de/en/entryprocesses</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:26.708Z</t>
+    <t>2026-10-22T00:09:14.880Z</t>
   </si>
   <si>
     <t>Entry regulations | Lufthansa</t>
@@ -967,7 +967,7 @@
     <t>de/en/europa-tarife-economy-class</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:28.714Z</t>
+    <t>2026-10-22T00:09:17.643Z</t>
   </si>
   <si>
     <t>Our Europe fares | Lufthansa</t>
@@ -982,7 +982,7 @@
     <t>de/en/europcar</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:31.567Z</t>
+    <t>2026-10-22T00:09:20.121Z</t>
   </si>
   <si>
     <t>Europcar | Lufthansa</t>
@@ -997,7 +997,7 @@
     <t>de/en/exclusive-charter</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:33.293Z</t>
+    <t>2026-10-22T00:09:21.997Z</t>
   </si>
   <si>
     <t>Lufthansa Charter | Lufthansa</t>
@@ -1012,7 +1012,7 @@
     <t>de/en/faq-ejournals</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:35.654Z</t>
+    <t>2026-10-22T00:09:27.901Z</t>
   </si>
   <si>
     <t>FAQs about eJournals | Lufthansa</t>
@@ -1033,7 +1033,7 @@
     <t>form</t>
   </si>
   <si>
-    <t>2026-10-21T22:35:24.617Z</t>
+    <t>2026-10-22T00:11:47.818Z</t>
   </si>
   <si>
     <t>Feedback and other contact forms | Lufthansa</t>
@@ -1048,7 +1048,7 @@
     <t>de/en/fia-valet-service</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:38.408Z</t>
+    <t>2026-10-22T00:09:29.894Z</t>
   </si>
   <si>
     <t>FIA Valet Service | Lufthansa</t>
@@ -1063,7 +1063,7 @@
     <t>de/en/first-class-comfort</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:43.359Z</t>
+    <t>2026-10-22T00:06:44.612Z</t>
   </si>
   <si>
     <t>Comfort on board First Class | Lufthansa</t>
@@ -1081,7 +1081,7 @@
     <t>de/en/first-class-lounges</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:48.150Z</t>
+    <t>2026-10-22T00:09:35.042Z</t>
   </si>
   <si>
     <t>First Class Lounges | Lufthansa</t>
@@ -1096,7 +1096,7 @@
     <t>de/en/first-class-personal-assistant</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:49.855Z</t>
+    <t>2026-10-22T00:09:37.147Z</t>
   </si>
   <si>
     <t>First Class personal assistant service | Lufthansa</t>
@@ -1111,7 +1111,7 @@
     <t>de/en/first-class-terminal</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:52.460Z</t>
+    <t>2026-10-22T00:09:39.159Z</t>
   </si>
   <si>
     <t>First Class Terminal | Lufthansa</t>
@@ -1126,7 +1126,7 @@
     <t>de/en/first-class-valet-parking-service</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:55.683Z</t>
+    <t>2026-10-22T00:09:40.962Z</t>
   </si>
   <si>
     <t>Valet parking service | Lufthansa</t>
@@ -1141,7 +1141,7 @@
     <t>de/en/first-class</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:40.870Z</t>
+    <t>2026-10-22T00:09:32.278Z</t>
   </si>
   <si>
     <t>Lufthansa First Class | Lufthansa</t>
@@ -1156,7 +1156,7 @@
     <t>de/en/fliegen-mit-baby</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:58.220Z</t>
+    <t>2026-10-22T00:09:42.814Z</t>
   </si>
   <si>
     <t>Flying with baby | Lufthansa</t>
@@ -1171,7 +1171,7 @@
     <t>de/en/flight-disruptions</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:00.710Z</t>
+    <t>2026-10-22T00:09:44.976Z</t>
   </si>
   <si>
     <t>Flights delayed and cancelled at short notice | Lufthansa</t>
@@ -1183,298 +1183,301 @@
     <t>de/en/flights.report.json</t>
   </si>
   <si>
+    <t>["columns-media","destination-finder"]</t>
+  </si>
+  <si>
+    <t>de/en/flights</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:04:55.864Z</t>
+  </si>
+  <si>
+    <t>Flight offers and destinations worldwide | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/flights</t>
+  </si>
+  <si>
+    <t>de/en/fly-more-sustainabl.report.json</t>
+  </si>
+  <si>
+    <t>de/en/fly-more-sustainabl</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:09:46.835Z</t>
+  </si>
+  <si>
+    <t>Fly more sustainably | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/fly-more-sustainabl</t>
+  </si>
+  <si>
+    <t>de/en/flying-with-small-children.report.json</t>
+  </si>
+  <si>
+    <t>de/en/flying-with-small-children</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:05:35.189Z</t>
+  </si>
+  <si>
+    <t>Flying with small children | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/flying-with-small-children</t>
+  </si>
+  <si>
+    <t>de/en/flynet.report.json</t>
+  </si>
+  <si>
+    <t>de/en/flynet</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:09:49.465Z</t>
+  </si>
+  <si>
+    <t>FlyNet® on board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/flynet</t>
+  </si>
+  <si>
+    <t>de/en/fmg-valet-parking-service.report.json</t>
+  </si>
+  <si>
+    <t>de/en/fmg-valet-parking-service</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:09:52.059Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/fmg-valet-parking-service</t>
+  </si>
+  <si>
+    <t>de/en/food-and-beverages.report.json</t>
+  </si>
+  <si>
+    <t>de/en/food-and-beverages</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:04:58.145Z</t>
+  </si>
+  <si>
+    <t>Menus on board | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/food-and-beverages</t>
+  </si>
+  <si>
+    <t>de/en/footer.report.json</t>
+  </si>
+  <si>
+    <t>de/en/footer</t>
+  </si>
+  <si>
+    <t>2026-10-21T17:54:45.381Z</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/homepage#footer</t>
+  </si>
+  <si>
+    <t>de/en/free2move.report.json</t>
+  </si>
+  <si>
+    <t>de/en/free2move</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:09:54.837Z</t>
+  </si>
+  <si>
+    <t>Free2move carsharing | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/free2move</t>
+  </si>
+  <si>
+    <t>de/en/freigepaeck-regeln.report.json</t>
+  </si>
+  <si>
+    <t>de/en/freigepaeck-regeln</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:09:57.113Z</t>
+  </si>
+  <si>
+    <t>Free baggage rules at Lufthansa | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/freigepaeck-regeln</t>
+  </si>
+  <si>
+    <t>de/en/gefaehrliche-gegenstaende.report.json</t>
+  </si>
+  <si>
+    <t>de/en/gefaehrliche-gegenstaende</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:09:59.313Z</t>
+  </si>
+  <si>
+    <t>Dangerous goods | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/gefaehrliche-gegenstaende</t>
+  </si>
+  <si>
+    <t>de/en/green-fare.report.json</t>
+  </si>
+  <si>
+    <t>de/en/green-fare</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:10:01.727Z</t>
+  </si>
+  <si>
+    <t>Green Fares: More sustainable air travel | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/green-fare</t>
+  </si>
+  <si>
+    <t>de/en/group-travel-and-charter.report.json</t>
+  </si>
+  <si>
+    <t>de/en/group-travel-and-charter</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:10:05.722Z</t>
+  </si>
+  <si>
+    <t>Group travel and Lufthansa Charter | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/group-travel-and-charter</t>
+  </si>
+  <si>
+    <t>de/en/group-travel.report.json</t>
+  </si>
+  <si>
+    <t>de/en/group-travel</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:10:03.836Z</t>
+  </si>
+  <si>
+    <t>Group travel | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/group-travel</t>
+  </si>
+  <si>
+    <t>de/en/hertz.report.json</t>
+  </si>
+  <si>
+    <t>de/en/hertz</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:10:07.633Z</t>
+  </si>
+  <si>
+    <t>Hertz | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/hertz</t>
+  </si>
+  <si>
+    <t>de/en/homepage.report.json</t>
+  </si>
+  <si>
+    <t>de/en/homepage</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:04:28.208Z</t>
+  </si>
+  <si>
+    <t>Book your flight now - travel with Lufthansa to over 200 destinations | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/homepage</t>
+  </si>
+  <si>
+    <t>de/en/hotel-offers.report.json</t>
+  </si>
+  <si>
+    <t>de/en/hotel-offers</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:10:10.361Z</t>
+  </si>
+  <si>
+    <t>Hotel offers | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/hotel-offers</t>
+  </si>
+  <si>
+    <t>de/en/imprint.report.json</t>
+  </si>
+  <si>
+    <t>["columns-media","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>de/en/imprint</t>
+  </si>
+  <si>
+    <t>legal</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:11:42.520Z</t>
+  </si>
+  <si>
+    <t>Legal notice | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/imprint</t>
+  </si>
+  <si>
+    <t>de/en/lh-rentalcar.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lh-rentalcar</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:10:13.117Z</t>
+  </si>
+  <si>
+    <t>Car rental partners | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lh-rentalcar</t>
+  </si>
+  <si>
+    <t>de/en/lounge-companions.report.json</t>
+  </si>
+  <si>
+    <t>de/en/lounge-companions</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:10:16.010Z</t>
+  </si>
+  <si>
+    <t>Take your companions into the lounge with you | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/lounge-companions</t>
+  </si>
+  <si>
+    <t>de/en/lounges.report.json</t>
+  </si>
+  <si>
     <t>["columns-media"]</t>
   </si>
   <si>
-    <t>de/en/flights</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:29:04.966Z</t>
-  </si>
-  <si>
-    <t>Flight offers and destinations worldwide | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/flights</t>
-  </si>
-  <si>
-    <t>de/en/fly-more-sustainabl.report.json</t>
-  </si>
-  <si>
-    <t>de/en/fly-more-sustainabl</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:02.743Z</t>
-  </si>
-  <si>
-    <t>Fly more sustainably | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/fly-more-sustainabl</t>
-  </si>
-  <si>
-    <t>de/en/flying-with-small-children.report.json</t>
-  </si>
-  <si>
-    <t>de/en/flying-with-small-children</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:29:44.690Z</t>
-  </si>
-  <si>
-    <t>Flying with small children | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/flying-with-small-children</t>
-  </si>
-  <si>
-    <t>de/en/flynet.report.json</t>
-  </si>
-  <si>
-    <t>de/en/flynet</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:05.112Z</t>
-  </si>
-  <si>
-    <t>FlyNet® on board | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/flynet</t>
-  </si>
-  <si>
-    <t>de/en/fmg-valet-parking-service.report.json</t>
-  </si>
-  <si>
-    <t>de/en/fmg-valet-parking-service</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:07.569Z</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/fmg-valet-parking-service</t>
-  </si>
-  <si>
-    <t>de/en/food-and-beverages.report.json</t>
-  </si>
-  <si>
-    <t>de/en/food-and-beverages</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:29:08.014Z</t>
-  </si>
-  <si>
-    <t>Menus on board | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/food-and-beverages</t>
-  </si>
-  <si>
-    <t>de/en/footer.report.json</t>
-  </si>
-  <si>
-    <t>de/en/footer</t>
-  </si>
-  <si>
-    <t>2026-10-21T17:54:45.381Z</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/homepage#footer</t>
-  </si>
-  <si>
-    <t>de/en/free2move.report.json</t>
-  </si>
-  <si>
-    <t>de/en/free2move</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:09.325Z</t>
-  </si>
-  <si>
-    <t>Free2move carsharing | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/free2move</t>
-  </si>
-  <si>
-    <t>de/en/freigepaeck-regeln.report.json</t>
-  </si>
-  <si>
-    <t>de/en/freigepaeck-regeln</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:12.161Z</t>
-  </si>
-  <si>
-    <t>Free baggage rules at Lufthansa | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/freigepaeck-regeln</t>
-  </si>
-  <si>
-    <t>de/en/gefaehrliche-gegenstaende.report.json</t>
-  </si>
-  <si>
-    <t>de/en/gefaehrliche-gegenstaende</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:14.892Z</t>
-  </si>
-  <si>
-    <t>Dangerous goods | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/gefaehrliche-gegenstaende</t>
-  </si>
-  <si>
-    <t>de/en/green-fare.report.json</t>
-  </si>
-  <si>
-    <t>de/en/green-fare</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:16.852Z</t>
-  </si>
-  <si>
-    <t>Green Fares: More sustainable air travel | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/green-fare</t>
-  </si>
-  <si>
-    <t>de/en/group-travel-and-charter.report.json</t>
-  </si>
-  <si>
-    <t>de/en/group-travel-and-charter</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:21.847Z</t>
-  </si>
-  <si>
-    <t>Group travel and Lufthansa Charter | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/group-travel-and-charter</t>
-  </si>
-  <si>
-    <t>de/en/group-travel.report.json</t>
-  </si>
-  <si>
-    <t>de/en/group-travel</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:19.066Z</t>
-  </si>
-  <si>
-    <t>Group travel | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/group-travel</t>
-  </si>
-  <si>
-    <t>de/en/hertz.report.json</t>
-  </si>
-  <si>
-    <t>de/en/hertz</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:24.343Z</t>
-  </si>
-  <si>
-    <t>Hertz | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/hertz</t>
-  </si>
-  <si>
-    <t>de/en/homepage.report.json</t>
-  </si>
-  <si>
-    <t>de/en/homepage</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:28:36.795Z</t>
-  </si>
-  <si>
-    <t>Book your flight now - travel with Lufthansa to over 200 destinations | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/homepage</t>
-  </si>
-  <si>
-    <t>de/en/hotel-offers.report.json</t>
-  </si>
-  <si>
-    <t>de/en/hotel-offers</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:26.676Z</t>
-  </si>
-  <si>
-    <t>Hotel offers | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/hotel-offers</t>
-  </si>
-  <si>
-    <t>de/en/imprint.report.json</t>
-  </si>
-  <si>
-    <t>["columns-media","columns-media","columns-media"]</t>
-  </si>
-  <si>
-    <t>de/en/imprint</t>
-  </si>
-  <si>
-    <t>legal</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:35:19.333Z</t>
-  </si>
-  <si>
-    <t>Legal notice | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/imprint</t>
-  </si>
-  <si>
-    <t>de/en/lh-rentalcar.report.json</t>
-  </si>
-  <si>
-    <t>de/en/lh-rentalcar</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:29.136Z</t>
-  </si>
-  <si>
-    <t>Car rental partners | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/lh-rentalcar</t>
-  </si>
-  <si>
-    <t>de/en/lounge-companions.report.json</t>
-  </si>
-  <si>
-    <t>de/en/lounge-companions</t>
-  </si>
-  <si>
-    <t>2026-10-21T22:33:31.893Z</t>
-  </si>
-  <si>
-    <t>Take your companions into the lounge with you | Lufthansa</t>
-  </si>
-  <si>
-    <t>https://www.lufthansa.com/de/en/lounge-companions</t>
-  </si>
-  <si>
-    <t>de/en/lounges.report.json</t>
-  </si>
-  <si>
     <t>de/en/lounges</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:12.311Z</t>
+    <t>2026-10-22T00:05:00.989Z</t>
   </si>
   <si>
     <t>Lounges | Lufthansa</t>
@@ -1489,7 +1492,7 @@
     <t>de/en/lufthansa-am-flughafen-frankfurt</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:33.693Z</t>
+    <t>2026-10-22T00:10:19.166Z</t>
   </si>
   <si>
     <t>Lufthansa at Frankfurt Airport | Lufthansa</t>
@@ -1504,7 +1507,7 @@
     <t>de/en/lufthansa-at-berlin-airport</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:36.028Z</t>
+    <t>2026-10-22T00:10:21.689Z</t>
   </si>
   <si>
     <t>Lufthansa at Berlin Brandenburg Airport | Lufthansa</t>
@@ -1519,7 +1522,7 @@
     <t>de/en/lufthansa-at-duesseldorf-airport</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:38.951Z</t>
+    <t>2026-10-22T00:10:24.152Z</t>
   </si>
   <si>
     <t>Lufthansa at Dusseldorf Airport | Lufthansa</t>
@@ -1534,7 +1537,7 @@
     <t>de/en/lufthansa-at-vienna-airport</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:41.420Z</t>
+    <t>2026-10-22T00:10:26.714Z</t>
   </si>
   <si>
     <t>Lufthansa at Vienna Airport | Lufthansa</t>
@@ -1549,7 +1552,7 @@
     <t>de/en/lufthansa-at-zuerich-airport</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:43.859Z</t>
+    <t>2026-10-22T00:10:28.780Z</t>
   </si>
   <si>
     <t>Lufthansa at Zurich Airport | Lufthansa</t>
@@ -1564,7 +1567,7 @@
     <t>de/en/lufthansa-aviation-group</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:45.803Z</t>
+    <t>2026-10-22T00:10:30.614Z</t>
   </si>
   <si>
     <t>Lufthansa Aviation Group | Lufthansa</t>
@@ -1579,7 +1582,7 @@
     <t>de/en/lufthansa-business-class-on-long-haul-routes</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:48.569Z</t>
+    <t>2026-10-22T00:10:32.917Z</t>
   </si>
   <si>
     <t>Business Class on long-haul routes | Lufthansa</t>
@@ -1594,7 +1597,7 @@
     <t>de/en/lufthansa-corporate-customers</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:50.458Z</t>
+    <t>2026-10-22T00:10:35.309Z</t>
   </si>
   <si>
     <t>Lufthansa for corporate customers | Lufthansa</t>
@@ -1609,7 +1612,7 @@
     <t>de/en/lufthansa-express-bus</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:54.761Z</t>
+    <t>2026-10-22T00:10:40.537Z</t>
   </si>
   <si>
     <t>Lufthansa Express Bus | Lufthansa</t>
@@ -1624,7 +1627,7 @@
     <t>de/en/lufthansa-express-rail</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:56.987Z</t>
+    <t>2026-10-22T00:10:43.135Z</t>
   </si>
   <si>
     <t>Lufthansa Express Rail | Lufthansa</t>
@@ -1639,7 +1642,7 @@
     <t>de/en/lufthansa-express</t>
   </si>
   <si>
-    <t>2026-10-21T22:33:52.450Z</t>
+    <t>2026-10-22T00:10:38.087Z</t>
   </si>
   <si>
     <t>Airport arrival and departure – travel seamlessly | Lufthansa</t>
@@ -1654,7 +1657,7 @@
     <t>de/en/lufthansa-first-class-entertainment</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:00.424Z</t>
+    <t>2026-10-22T00:06:47.775Z</t>
   </si>
   <si>
     <t>Entertainment world | Lufthansa</t>
@@ -1669,7 +1672,7 @@
     <t>de/en/lufthansa-group-star-alliance-and-partner-airlines</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:05.613Z</t>
+    <t>2026-10-22T00:10:45.276Z</t>
   </si>
   <si>
     <t>Lufthansa Group, Star Alliance and partner airlines | Lufthansa</t>
@@ -1684,7 +1687,7 @@
     <t>de/en/lufthansa-guide-service</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:07.304Z</t>
+    <t>2026-10-22T00:10:47.767Z</t>
   </si>
   <si>
     <t>Lufthansa Guide Service Munich | Lufthansa</t>
@@ -1699,7 +1702,7 @@
     <t>de/en/lufthansa-terminal-muenchen</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:10.267Z</t>
+    <t>2026-10-22T00:10:49.726Z</t>
   </si>
   <si>
     <t>Lufthansa at Munich Airport | Lufthansa</t>
@@ -1714,7 +1717,7 @@
     <t>de/en/lufthansa-travel-classes</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:15.410Z</t>
+    <t>2026-10-22T00:05:03.334Z</t>
   </si>
   <si>
     <t>Our travel classes | Lufthansa</t>
@@ -1729,7 +1732,7 @@
     <t>de/en/medikamenten-transport</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:13.158Z</t>
+    <t>2026-10-22T00:10:51.521Z</t>
   </si>
   <si>
     <t>Always at the right temperature | Lufthansa</t>
@@ -1744,7 +1747,7 @@
     <t>de/en/meetings-and-events-delegates</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:15.050Z</t>
+    <t>2026-10-22T00:10:54.712Z</t>
   </si>
   <si>
     <t>Meetings &amp; Events: Information for organisers | Lufthansa</t>
@@ -1759,7 +1762,7 @@
     <t>de/en/meetings-and-events-organisers</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:16.965Z</t>
+    <t>2026-10-22T00:10:57.013Z</t>
   </si>
   <si>
     <t>Meeting &amp; Events: Information for organisers | Lufthansa</t>
@@ -1774,7 +1777,7 @@
     <t>de/en/meetings-and-events</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:17.390Z</t>
+    <t>2026-10-22T00:05:06.009Z</t>
   </si>
   <si>
     <t>Lufthansa Group Meetings &amp; Events | Lufthansa</t>
@@ -1789,7 +1792,7 @@
     <t>de/en/menus-on-long-haul-flights</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:18.943Z</t>
+    <t>2026-10-22T00:06:18.059Z</t>
   </si>
   <si>
     <t>Menus on long-haul flights | Lufthansa</t>
@@ -1804,7 +1807,7 @@
     <t>de/en/menus-travel-classes</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:23.793Z</t>
+    <t>2026-10-22T00:06:20.334Z</t>
   </si>
   <si>
     <t>Menus in our travel classes | Lufthansa</t>
@@ -1819,7 +1822,7 @@
     <t>de/en/miles-and-more</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:19.875Z</t>
+    <t>2026-10-22T00:05:07.811Z</t>
   </si>
   <si>
     <t>Miles &amp; More – Our frequent flyer programme | Lufthansa</t>
@@ -1834,7 +1837,7 @@
     <t>de/en/mobility-partner-program-healthcare</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:27.573Z</t>
+    <t>2026-10-22T00:10:59.912Z</t>
   </si>
   <si>
     <t>Lufthansa Global Healthcare and Medical Services | Lufthansa</t>
@@ -1861,7 +1864,7 @@
     <t>de/en/onboard-delights</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:30.374Z</t>
+    <t>2026-10-22T00:06:23.249Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/onboard-delights</t>
@@ -1873,7 +1876,7 @@
     <t>de/en/online-check-in-info</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:34.662Z</t>
+    <t>2026-10-22T00:11:05.478Z</t>
   </si>
   <si>
     <t>Online check-in information | Lufthansa</t>
@@ -1894,7 +1897,7 @@
     <t>app-entry</t>
   </si>
   <si>
-    <t>2026-10-21T22:35:29.211Z</t>
+    <t>2026-10-22T00:11:53.146Z</t>
   </si>
   <si>
     <t>Online check-in | Lufthansa</t>
@@ -1909,7 +1912,7 @@
     <t>de/en/overview-flights</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:22.394Z</t>
+    <t>2026-10-22T00:05:10.218Z</t>
   </si>
   <si>
     <t>Flights – your journey starts here | Lufthansa</t>
@@ -1927,7 +1930,7 @@
     <t>de/en/overview-manage</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:24.956Z</t>
+    <t>2026-10-22T00:05:12.295Z</t>
   </si>
   <si>
     <t>Manage your bookings | Lufthansa</t>
@@ -1942,7 +1945,7 @@
     <t>de/en/overview-special-request</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:26.725Z</t>
+    <t>2026-10-22T00:05:14.409Z</t>
   </si>
   <si>
     <t>Special requests | Lufthansa</t>
@@ -1957,7 +1960,7 @@
     <t>de/en/overview-travel-information</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:29.135Z</t>
+    <t>2026-10-22T00:05:17.148Z</t>
   </si>
   <si>
     <t>Travel information – what you need to know | Lufthansa</t>
@@ -1972,7 +1975,7 @@
     <t>de/en/partner</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:37.659Z</t>
+    <t>2026-10-22T00:11:08.021Z</t>
   </si>
   <si>
     <t>Partners | Lufthansa</t>
@@ -1987,7 +1990,7 @@
     <t>de/en/passenger-receipt-90</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:39.755Z</t>
+    <t>2026-10-22T00:11:10.441Z</t>
   </si>
   <si>
     <t>Passenger receipt | Lufthansa</t>
@@ -2002,7 +2005,7 @@
     <t>de/en/passengers-using-wheelchairs</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:42.001Z</t>
+    <t>2026-10-22T00:11:12.569Z</t>
   </si>
   <si>
     <t>Passengers requiring wheelchairs | Lufthansa</t>
@@ -2011,13 +2014,58 @@
     <t>https://www.lufthansa.com/de/en/passengers-using-wheelchairs</t>
   </si>
   <si>
+    <t>de/en/passengers-with-sensory-impairment.report.json</t>
+  </si>
+  <si>
+    <t>de/en/passengers-with-sensory-impairment</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:02:44.087Z</t>
+  </si>
+  <si>
+    <t>Passengers with sensory impairments | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/passengers-with-sensory-impairment</t>
+  </si>
+  <si>
+    <t>de/en/payment-options-at-the-airport.report.json</t>
+  </si>
+  <si>
+    <t>de/en/payment-options-at-the-airport</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:02:46.372Z</t>
+  </si>
+  <si>
+    <t>Payment options at the airport | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/payment-options-at-the-airport</t>
+  </si>
+  <si>
+    <t>de/en/premium-economy-class.report.json</t>
+  </si>
+  <si>
+    <t>de/en/premium-economy-class</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:02:49.212Z</t>
+  </si>
+  <si>
+    <t>Premium Economy Class | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/premium-economy-class</t>
+  </si>
+  <si>
     <t>de/en/services-at-the-airport.report.json</t>
   </si>
   <si>
     <t>de/en/services-at-the-airport</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:32.371Z</t>
+    <t>2026-10-22T00:05:19.979Z</t>
   </si>
   <si>
     <t>Services at the airport | Lufthansa</t>
@@ -2032,7 +2080,7 @@
     <t>de/en/services-on-board</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:34.558Z</t>
+    <t>2026-10-22T00:05:21.812Z</t>
   </si>
   <si>
     <t>Services on board | Lufthansa</t>
@@ -2047,7 +2095,7 @@
     <t>de/en/special-needs</t>
   </si>
   <si>
-    <t>2026-10-21T22:29:39.318Z</t>
+    <t>2026-10-22T00:05:24.843Z</t>
   </si>
   <si>
     <t>Register your assistance requirements online | Lufthansa</t>
@@ -2068,7 +2116,7 @@
     <t>flight-status</t>
   </si>
   <si>
-    <t>2026-10-21T17:01:33.445Z</t>
+    <t>2026-10-21T22:35:34.539Z</t>
   </si>
   <si>
     <t>Timetable &amp; flight status | Lufthansa</t>
@@ -2083,7 +2131,7 @@
     <t>de/en/unterhaltung-an-bord</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:44.190Z</t>
+    <t>2026-10-22T00:06:51.162Z</t>
   </si>
   <si>
     <t>Entertainment on board | Lufthansa</t>
@@ -2110,7 +2158,7 @@
     <t>gb/en/homepage</t>
   </si>
   <si>
-    <t>2026-10-21T22:28:46.096Z</t>
+    <t>2026-10-22T00:04:38.121Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/gb/en/homepage</t>
@@ -2140,7 +2188,7 @@
     <t>aircore-destination-overview</t>
   </si>
   <si>
-    <t>2026-10-21T16:55:43.571Z</t>
+    <t>2026-10-21T22:35:43.227Z</t>
   </si>
   <si>
     <t>Book flights to destinations all over the world | Lufthansa</t>
@@ -2173,7 +2221,7 @@
     <t>de/de/discover-lufthansa/new-onboard-experience</t>
   </si>
   <si>
-    <t>2026-10-21T22:35:03.116Z</t>
+    <t>2026-10-22T00:11:27.425Z</t>
   </si>
   <si>
     <t>New Onboard Experience | Lufthansa</t>
@@ -2188,7 +2236,7 @@
     <t>de/de/during-your-trip/lhg-wifi</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:18.873Z</t>
+    <t>2026-10-22T00:06:58.327Z</t>
   </si>
   <si>
     <t>Lufthansa Group Wi-Fi | Lufthansa</t>
@@ -2215,7 +2263,7 @@
     <t>de/en/book-and-manage/pax-receipt</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:46.923Z</t>
+    <t>2026-10-22T00:08:09.418Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/book-and-manage/pax-receipt</t>
@@ -2227,7 +2275,7 @@
     <t>de/en/book-and-manage/rebook</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:52.704Z</t>
+    <t>2026-10-22T00:08:15.509Z</t>
   </si>
   <si>
     <t>Flight Rebooking | Lufthansa</t>
@@ -2242,7 +2290,7 @@
     <t>de/en/discover-lufthansa/flightreservation-priceguarantee</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:51.511Z</t>
+    <t>2026-10-22T00:09:01.308Z</t>
   </si>
   <si>
     <t>Reservation with price guarantee | Lufthansa</t>
@@ -2257,7 +2305,7 @@
     <t>de/en/discover-lufthansa/miles-and-more-credit-card</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:56.206Z</t>
+    <t>2026-10-22T00:09:05.869Z</t>
   </si>
   <si>
     <t>Miles &amp; More Credit Card | Lufthansa</t>
@@ -2272,7 +2320,7 @@
     <t>de/en/discover-lufthansa/new-onboard-experience</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:59.894Z</t>
+    <t>2026-10-22T00:11:22.313Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/discover-lufthansa/new-onboard-experience</t>
@@ -2284,7 +2332,7 @@
     <t>de/en/during-your-trip/internet-overview</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:14.040Z</t>
+    <t>2026-10-22T00:09:09.109Z</t>
   </si>
   <si>
     <t>Internet | Lufthansa</t>
@@ -2299,7 +2347,7 @@
     <t>de/en/during-your-trip/lhg-wifi</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:16.809Z</t>
+    <t>2026-10-22T00:06:42.517Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/during-your-trip/lhg-wifi</t>
@@ -2317,6 +2365,21 @@
     <t>https://www.lufthansa.com/de/en/homepage#payment-social</t>
   </si>
   <si>
+    <t>de/en/prepare-for-your-trip/current-travel-information.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/current-travel-information</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:04.692Z</t>
+  </si>
+  <si>
+    <t>Current information | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/current-travel-information</t>
+  </si>
+  <si>
     <t>gb/en/fragments/payment-social.report.json</t>
   </si>
   <si>
@@ -2359,7 +2422,7 @@
     <t>de/de/100-years/history/menu-on-board</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:57.145Z</t>
+    <t>2026-10-22T00:11:24.603Z</t>
   </si>
   <si>
     <t>Menüs an Board | Lufthansa</t>
@@ -2374,7 +2437,7 @@
     <t>de/en/100-years/history/menu-on-board</t>
   </si>
   <si>
-    <t>2026-10-21T22:34:54.910Z</t>
+    <t>2026-10-22T00:11:20.013Z</t>
   </si>
   <si>
     <t>Menus on Board | Lufthansa</t>
@@ -2395,7 +2458,7 @@
     <t>insights</t>
   </si>
   <si>
-    <t>2026-10-21T22:35:13.632Z</t>
+    <t>2026-10-22T00:11:37.732Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/articles/explore-the-world/eat-see-do-berlin</t>
@@ -2407,7 +2470,7 @@
     <t>de/en/book-and-manage/additional-services/get-your-guide</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:23.858Z</t>
+    <t>2026-10-22T00:07:11.959Z</t>
   </si>
   <si>
     <t>Unforgettable travel experiences—GetYourGuide | Lufthansa</t>
@@ -2422,7 +2485,7 @@
     <t>de/en/book-and-manage/additional-services/travel-insurances</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:26.033Z</t>
+    <t>2026-10-22T00:07:45.560Z</t>
   </si>
   <si>
     <t>Travel Care | Lufthansa</t>
@@ -2437,7 +2500,7 @@
     <t>de/en/book-and-manage/digital-self-services/airline-apps</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:27.759Z</t>
+    <t>2026-10-22T00:07:47.485Z</t>
   </si>
   <si>
     <t>Simply travel smarter | Lufthansa</t>
@@ -2452,7 +2515,7 @@
     <t>de/en/book-and-manage/flights/air-baltic</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:30.294Z</t>
+    <t>2026-10-22T00:07:49.358Z</t>
   </si>
   <si>
     <t>Your Lufthansa flight with airBaltic | Lufthansa</t>
@@ -2467,7 +2530,7 @@
     <t>de/en/book-and-manage/flights/ana</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:32.649Z</t>
+    <t>2026-10-22T00:07:52.528Z</t>
   </si>
   <si>
     <t>ANA | Lufthansa</t>
@@ -2485,7 +2548,7 @@
     <t>de/en/book-and-manage/flights/giftvoucher</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:37.799Z</t>
+    <t>2026-10-22T00:07:58.155Z</t>
   </si>
   <si>
     <t>Buy a Lufthansa Gift Card &amp; give a flight as a gift | Lufthansa</t>
@@ -2500,7 +2563,7 @@
     <t>de/en/book-and-manage/flights/helvetic</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:40.563Z</t>
+    <t>2026-10-22T00:08:01.265Z</t>
   </si>
   <si>
     <t>Helvetic | Lufthansa</t>
@@ -2515,7 +2578,7 @@
     <t>de/en/book-and-manage/flights/lufthansa-voucher</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:43.081Z</t>
+    <t>2026-10-22T00:08:04.594Z</t>
   </si>
   <si>
     <t>Terms of use for the purchase of Gift Vouchers | Lufthansa</t>
@@ -2530,7 +2593,7 @@
     <t>de/en/book-and-manage/flights/wetlease-hub</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:44.869Z</t>
+    <t>2026-10-22T00:08:06.876Z</t>
   </si>
   <si>
     <t>Wet lease flights | Lufthansa</t>
@@ -2545,7 +2608,7 @@
     <t>de/en/book-and-manage/pax-receipt/invoices-different-countries</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:49.989Z</t>
+    <t>2026-10-22T00:08:12.195Z</t>
   </si>
   <si>
     <t>Invoices for different countries | Lufthansa</t>
@@ -2560,7 +2623,7 @@
     <t>de/en/book-and-manage/rebook/involuntary-rebooking</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:55.679Z</t>
+    <t>2026-10-22T00:08:17.951Z</t>
   </si>
   <si>
     <t>Flight cancellation | Lufthansa</t>
@@ -2575,7 +2638,7 @@
     <t>de/en/book-and-manage/rebook/voluntary-rebooking</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:57.574Z</t>
+    <t>2026-10-22T00:08:19.994Z</t>
   </si>
   <si>
     <t>Change flight | Lufthansa</t>
@@ -2590,7 +2653,7 @@
     <t>de/en/discover-lufthansa/carbon-offsetting/climate-protection-projects</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:42.262Z</t>
+    <t>2026-10-22T00:08:51.031Z</t>
   </si>
   <si>
     <t>Climate protection projects | Lufthansa</t>
@@ -2605,7 +2668,7 @@
     <t>de/en/discover-lufthansa/carbon-offsetting/environmental-cost-surcharge</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:44.526Z</t>
+    <t>2026-10-22T00:08:53.029Z</t>
   </si>
   <si>
     <t>Environmental Cost Surcharge | Lufthansa</t>
@@ -2620,7 +2683,7 @@
     <t>de/en/discover-lufthansa/carbon-offsetting/faq-saf</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:47.219Z</t>
+    <t>2026-10-22T00:08:55.725Z</t>
   </si>
   <si>
     <t>FAQs Sustainable Aviation Fuel | Lufthansa</t>
@@ -2635,7 +2698,7 @@
     <t>de/en/discover-lufthansa/carbon-offsetting/saf</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:49.735Z</t>
+    <t>2026-10-22T00:08:58.866Z</t>
   </si>
   <si>
     <t>Why support the use of Sustainable Aviation Fuel? | Lufthansa</t>
@@ -2650,7 +2713,7 @@
     <t>de/en/discover-lufthansa/lufthansa-group-airlines/ita-airways</t>
   </si>
   <si>
-    <t>2026-10-21T22:31:53.994Z</t>
+    <t>2026-10-22T00:09:03.946Z</t>
   </si>
   <si>
     <t>ITA Airways | Lufthansa</t>
@@ -2659,6 +2722,96 @@
     <t>https://www.lufthansa.com/de/en/discover-lufthansa/lufthansa-group-airlines/ita-airways</t>
   </si>
   <si>
+    <t>de/en/prepare-for-your-trip/baggage/electronic-devices-and-batteries.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/baggage/electronic-devices-and-batteries</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:01.487Z</t>
+  </si>
+  <si>
+    <t>Electronic devices and batteries | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/baggage/electronic-devices-and-batteries</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/entry-regulations/immigration-regulations-uk.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/entry-regulations/immigration-regulations-uk</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:09.673Z</t>
+  </si>
+  <si>
+    <t>New entry regulations for the United Kingdom | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/entry-regulations/immigration-regulations-uk</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/getting-to-and-from-the-airport/lufthansa-express-bus-briefing.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/getting-to-and-from-the-airport/lufthansa-express-bus-briefing</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:11.398Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Express Bus – assuring your journey | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/getting-to-and-from-the-airport/lufthansa-express-bus-briefing</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/getting-to-and-from-the-airport/lufthansa-express-rail-briefing.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/getting-to-and-from-the-airport/lufthansa-express-rail-briefing</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:13.929Z</t>
+  </si>
+  <si>
+    <t>Lufthansa Express Rail – assuring your journey | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/getting-to-and-from-the-airport/lufthansa-express-rail-briefing</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/medical-travel-companions.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/medical-travel-companions</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:16.155Z</t>
+  </si>
+  <si>
+    <t>Medical travel companions | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/special-travel-needs/medical-travel-companions</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/travel-classes/economy-basic.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/travel-classes/economy-basic</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:28.522Z</t>
+  </si>
+  <si>
+    <t>Economy Basic | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/travel-classes/economy-basic</t>
+  </si>
+  <si>
     <t>de/en/book-and-manage/flights/ana/faq.report.json</t>
   </si>
   <si>
@@ -2668,7 +2821,7 @@
     <t>de/en/book-and-manage/flights/ana/faq</t>
   </si>
   <si>
-    <t>2026-10-21T22:30:35.269Z</t>
+    <t>2026-10-22T00:07:55.317Z</t>
   </si>
   <si>
     <t>FAQs on travel with Lufthansa and ANA | Lufthansa</t>
@@ -2683,7 +2836,7 @@
     <t>de/en/during-your-trip/food-and-beverages/onboard-delights/faq</t>
   </si>
   <si>
-    <t>2026-10-21T22:32:08.618Z</t>
+    <t>2026-10-22T00:06:15.396Z</t>
   </si>
   <si>
     <t>FAQs | Lufthansa</t>
@@ -2692,6 +2845,126 @@
     <t>https://www.lufthansa.com/de/en/during-your-trip/food-and-beverages/onboard-delights/faq</t>
   </si>
   <si>
+    <t>de/en/prepare-for-your-trip/baggage/baggage-irregularities/delayed-baggage-lhg.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/baggage/baggage-irregularities/delayed-baggage-lhg</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:02:51.834Z</t>
+  </si>
+  <si>
+    <t>Delayed baggage lhg | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/baggage/baggage-irregularities/delayed-baggage-lhg</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/baggage/baggage-irregularities/faq-baggage-delay.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/baggage/baggage-irregularities/faq-baggage-delay</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:02:55.363Z</t>
+  </si>
+  <si>
+    <t>Frequently asked questions about delayed baggage | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/baggage/baggage-irregularities/faq-baggage-delay</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/baggage/baggage-irregularities/faq-damaged-baggage.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/baggage/baggage-irregularities/faq-damaged-baggage</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:02:58.415Z</t>
+  </si>
+  <si>
+    <t>Frequently asked questions about damaged baggage | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/baggage/baggage-irregularities/faq-damaged-baggage</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/entry-regulations/entering-schengen/entry-exit-system.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/entry-regulations/entering-schengen/entry-exit-system</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:07.347Z</t>
+  </si>
+  <si>
+    <t>EES: the European Union’s new Entry/Exit System | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/entry-regulations/entering-schengen/entry-exit-system</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/cognitive-impairment.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/cognitive-impairment</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:18.292Z</t>
+  </si>
+  <si>
+    <t>Cognitive impairments | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/cognitive-impairment</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/hearing-impairment.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/hearing-impairment</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:20.474Z</t>
+  </si>
+  <si>
+    <t>Hearing impairments | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/hearing-impairment</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/travel-companion.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/travel-companion</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:23.312Z</t>
+  </si>
+  <si>
+    <t>Travelling with a companion | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/travel-companion</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/visual-impairment.report.json</t>
+  </si>
+  <si>
+    <t>de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/visual-impairment</t>
+  </si>
+  <si>
+    <t>2026-10-22T00:03:26.446Z</t>
+  </si>
+  <si>
+    <t>Visual impairments | Lufthansa</t>
+  </si>
+  <si>
+    <t>https://www.lufthansa.com/de/en/prepare-for-your-trip/special-travel-needs/travel-with-needs/visual-impairment</t>
+  </si>
+  <si>
     <t>lhg/de/en/dest/cy/new-york.report.json</t>
   </si>
   <si>
@@ -2701,7 +2974,7 @@
     <t>lhg/de/en/dest/cy/new-york</t>
   </si>
   <si>
-    <t>2026-10-21T17:07:20.550Z</t>
+    <t>2026-10-21T22:35:49.019Z</t>
   </si>
   <si>
     <t>Flight to New York (NYC) | Lufthansa</t>
@@ -2722,7 +2995,7 @@
     <t>aircore-route</t>
   </si>
   <si>
-    <t>2026-10-21T17:07:24.799Z</t>
+    <t>2026-10-21T22:35:55.034Z</t>
   </si>
   <si>
     <t>Flights from Germany to USA | Lufthansa</t>
@@ -3117,7 +3390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I193"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -5801,13 +6074,13 @@
         <v>485</v>
       </c>
       <c r="B93" t="s">
-        <v>390</v>
+        <v>486</v>
       </c>
       <c r="C93" t="s">
         <v>10</v>
       </c>
       <c r="D93" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E93" t="s">
         <v>13</v>
@@ -5816,18 +6089,18 @@
         <v>98</v>
       </c>
       <c r="G93" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H93" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I93" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s">
         <v>36</v>
@@ -5836,7 +6109,7 @@
         <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E94" t="s">
         <v>13</v>
@@ -5845,18 +6118,18 @@
         <v>31</v>
       </c>
       <c r="G94" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H94" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I94" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B95" t="s">
         <v>36</v>
@@ -5865,7 +6138,7 @@
         <v>10</v>
       </c>
       <c r="D95" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E95" t="s">
         <v>13</v>
@@ -5874,18 +6147,18 @@
         <v>31</v>
       </c>
       <c r="G95" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H95" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I95" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s">
         <v>84</v>
@@ -5894,7 +6167,7 @@
         <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E96" t="s">
         <v>13</v>
@@ -5903,18 +6176,18 @@
         <v>31</v>
       </c>
       <c r="G96" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H96" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I96" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s">
         <v>84</v>
@@ -5923,7 +6196,7 @@
         <v>10</v>
       </c>
       <c r="D97" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E97" t="s">
         <v>13</v>
@@ -5932,18 +6205,18 @@
         <v>31</v>
       </c>
       <c r="G97" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H97" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I97" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B98" t="s">
         <v>84</v>
@@ -5952,7 +6225,7 @@
         <v>10</v>
       </c>
       <c r="D98" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E98" t="s">
         <v>13</v>
@@ -5961,18 +6234,18 @@
         <v>31</v>
       </c>
       <c r="G98" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H98" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I98" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B99" t="s">
         <v>36</v>
@@ -5981,7 +6254,7 @@
         <v>10</v>
       </c>
       <c r="D99" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E99" t="s">
         <v>13</v>
@@ -5990,18 +6263,18 @@
         <v>31</v>
       </c>
       <c r="G99" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H99" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I99" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B100" t="s">
         <v>36</v>
@@ -6010,7 +6283,7 @@
         <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E100" t="s">
         <v>13</v>
@@ -6019,18 +6292,18 @@
         <v>31</v>
       </c>
       <c r="G100" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H100" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I100" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B101" t="s">
         <v>36</v>
@@ -6039,7 +6312,7 @@
         <v>10</v>
       </c>
       <c r="D101" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E101" t="s">
         <v>13</v>
@@ -6048,18 +6321,18 @@
         <v>31</v>
       </c>
       <c r="G101" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H101" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I101" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B102" t="s">
         <v>237</v>
@@ -6068,7 +6341,7 @@
         <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E102" t="s">
         <v>13</v>
@@ -6077,18 +6350,18 @@
         <v>31</v>
       </c>
       <c r="G102" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H102" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I102" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B103" t="s">
         <v>84</v>
@@ -6097,7 +6370,7 @@
         <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E103" t="s">
         <v>13</v>
@@ -6106,18 +6379,18 @@
         <v>31</v>
       </c>
       <c r="G103" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H103" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I103" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B104" t="s">
         <v>36</v>
@@ -6126,7 +6399,7 @@
         <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E104" t="s">
         <v>13</v>
@@ -6135,18 +6408,18 @@
         <v>31</v>
       </c>
       <c r="G104" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H104" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I104" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B105" t="s">
         <v>36</v>
@@ -6155,7 +6428,7 @@
         <v>10</v>
       </c>
       <c r="D105" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E105" t="s">
         <v>13</v>
@@ -6164,18 +6437,18 @@
         <v>31</v>
       </c>
       <c r="G105" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H105" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I105" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B106" t="s">
         <v>36</v>
@@ -6184,7 +6457,7 @@
         <v>10</v>
       </c>
       <c r="D106" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E106" t="s">
         <v>13</v>
@@ -6193,18 +6466,18 @@
         <v>31</v>
       </c>
       <c r="G106" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H106" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I106" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B107" t="s">
         <v>36</v>
@@ -6213,7 +6486,7 @@
         <v>10</v>
       </c>
       <c r="D107" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E107" t="s">
         <v>13</v>
@@ -6222,18 +6495,18 @@
         <v>31</v>
       </c>
       <c r="G107" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H107" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I107" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B108" t="s">
         <v>36</v>
@@ -6242,7 +6515,7 @@
         <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E108" t="s">
         <v>13</v>
@@ -6251,18 +6524,18 @@
         <v>31</v>
       </c>
       <c r="G108" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H108" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I108" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s">
         <v>103</v>
@@ -6271,7 +6544,7 @@
         <v>10</v>
       </c>
       <c r="D109" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E109" t="s">
         <v>13</v>
@@ -6280,18 +6553,18 @@
         <v>98</v>
       </c>
       <c r="G109" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H109" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I109" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B110" t="s">
         <v>36</v>
@@ -6300,7 +6573,7 @@
         <v>10</v>
       </c>
       <c r="D110" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E110" t="s">
         <v>13</v>
@@ -6309,18 +6582,18 @@
         <v>31</v>
       </c>
       <c r="G110" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H110" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I110" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B111" t="s">
         <v>36</v>
@@ -6329,7 +6602,7 @@
         <v>10</v>
       </c>
       <c r="D111" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E111" t="s">
         <v>13</v>
@@ -6338,18 +6611,18 @@
         <v>31</v>
       </c>
       <c r="G111" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H111" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I111" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B112" t="s">
         <v>36</v>
@@ -6358,7 +6631,7 @@
         <v>10</v>
       </c>
       <c r="D112" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E112" t="s">
         <v>13</v>
@@ -6367,18 +6640,18 @@
         <v>31</v>
       </c>
       <c r="G112" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H112" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I112" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B113" t="s">
         <v>36</v>
@@ -6387,7 +6660,7 @@
         <v>10</v>
       </c>
       <c r="D113" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E113" t="s">
         <v>13</v>
@@ -6396,18 +6669,18 @@
         <v>98</v>
       </c>
       <c r="G113" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H113" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I113" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B114" t="s">
         <v>36</v>
@@ -6416,7 +6689,7 @@
         <v>10</v>
       </c>
       <c r="D114" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E114" t="s">
         <v>13</v>
@@ -6425,18 +6698,18 @@
         <v>31</v>
       </c>
       <c r="G114" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H114" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I114" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B115" t="s">
         <v>36</v>
@@ -6445,7 +6718,7 @@
         <v>10</v>
       </c>
       <c r="D115" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E115" t="s">
         <v>13</v>
@@ -6454,18 +6727,18 @@
         <v>31</v>
       </c>
       <c r="G115" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H115" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I115" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B116" t="s">
         <v>36</v>
@@ -6474,7 +6747,7 @@
         <v>10</v>
       </c>
       <c r="D116" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E116" t="s">
         <v>13</v>
@@ -6483,18 +6756,18 @@
         <v>98</v>
       </c>
       <c r="G116" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H116" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I116" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B117" t="s">
         <v>36</v>
@@ -6503,7 +6776,7 @@
         <v>10</v>
       </c>
       <c r="D117" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E117" t="s">
         <v>13</v>
@@ -6512,18 +6785,18 @@
         <v>31</v>
       </c>
       <c r="G117" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H117" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I117" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B118" t="s">
         <v>10</v>
@@ -6532,7 +6805,7 @@
         <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E118" t="s">
         <v>13</v>
@@ -6541,18 +6814,18 @@
         <v>14</v>
       </c>
       <c r="G118" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H118" t="s">
         <v>10</v>
       </c>
       <c r="I118" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B119" t="s">
         <v>90</v>
@@ -6561,7 +6834,7 @@
         <v>10</v>
       </c>
       <c r="D119" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E119" t="s">
         <v>13</v>
@@ -6570,18 +6843,18 @@
         <v>31</v>
       </c>
       <c r="G119" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H119" t="s">
         <v>93</v>
       </c>
       <c r="I119" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B120" t="s">
         <v>36</v>
@@ -6590,7 +6863,7 @@
         <v>10</v>
       </c>
       <c r="D120" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E120" t="s">
         <v>13</v>
@@ -6599,47 +6872,47 @@
         <v>31</v>
       </c>
       <c r="G120" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H120" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I120" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B121" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C121" t="s">
         <v>10</v>
       </c>
       <c r="D121" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E121" t="s">
         <v>13</v>
       </c>
       <c r="F121" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G121" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H121" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I121" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B122" t="s">
         <v>96</v>
@@ -6648,7 +6921,7 @@
         <v>10</v>
       </c>
       <c r="D122" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E122" t="s">
         <v>13</v>
@@ -6657,27 +6930,27 @@
         <v>98</v>
       </c>
       <c r="G122" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H122" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I122" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B123" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C123" t="s">
         <v>10</v>
       </c>
       <c r="D123" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E123" t="s">
         <v>13</v>
@@ -6686,18 +6959,18 @@
         <v>98</v>
       </c>
       <c r="G123" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H123" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I123" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B124" t="s">
         <v>96</v>
@@ -6706,7 +6979,7 @@
         <v>10</v>
       </c>
       <c r="D124" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E124" t="s">
         <v>13</v>
@@ -6715,18 +6988,18 @@
         <v>98</v>
       </c>
       <c r="G124" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H124" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I124" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B125" t="s">
         <v>36</v>
@@ -6735,7 +7008,7 @@
         <v>10</v>
       </c>
       <c r="D125" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E125" t="s">
         <v>13</v>
@@ -6744,18 +7017,18 @@
         <v>98</v>
       </c>
       <c r="G125" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H125" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I125" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B126" t="s">
         <v>36</v>
@@ -6764,7 +7037,7 @@
         <v>10</v>
       </c>
       <c r="D126" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E126" t="s">
         <v>13</v>
@@ -6773,18 +7046,18 @@
         <v>31</v>
       </c>
       <c r="G126" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H126" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I126" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B127" t="s">
         <v>36</v>
@@ -6793,7 +7066,7 @@
         <v>10</v>
       </c>
       <c r="D127" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E127" t="s">
         <v>13</v>
@@ -6802,18 +7075,18 @@
         <v>31</v>
       </c>
       <c r="G127" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H127" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I127" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B128" t="s">
         <v>237</v>
@@ -6822,7 +7095,7 @@
         <v>10</v>
       </c>
       <c r="D128" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E128" t="s">
         <v>13</v>
@@ -6831,18 +7104,18 @@
         <v>31</v>
       </c>
       <c r="G128" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H128" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I128" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B129" t="s">
         <v>36</v>
@@ -6851,56 +7124,56 @@
         <v>10</v>
       </c>
       <c r="D129" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E129" t="s">
         <v>13</v>
       </c>
       <c r="F129" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G129" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H129" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I129" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B130" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="C130" t="s">
         <v>10</v>
       </c>
       <c r="D130" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E130" t="s">
         <v>13</v>
       </c>
       <c r="F130" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G130" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H130" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I130" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B131" t="s">
         <v>36</v>
@@ -6909,30 +7182,30 @@
         <v>10</v>
       </c>
       <c r="D131" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E131" t="s">
         <v>13</v>
       </c>
       <c r="F131" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G131" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H131" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I131" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B132" t="s">
-        <v>682</v>
+        <v>36</v>
       </c>
       <c r="C132" t="s">
         <v>10</v>
@@ -6944,71 +7217,71 @@
         <v>13</v>
       </c>
       <c r="F132" t="s">
+        <v>98</v>
+      </c>
+      <c r="G132" t="s">
         <v>684</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>685</v>
       </c>
-      <c r="H132" t="s">
+      <c r="I132" t="s">
         <v>686</v>
-      </c>
-      <c r="I132" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>687</v>
+      </c>
+      <c r="B133" t="s">
+        <v>96</v>
+      </c>
+      <c r="C133" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" t="s">
         <v>688</v>
       </c>
-      <c r="B133" t="s">
-        <v>36</v>
-      </c>
-      <c r="C133" t="s">
-        <v>10</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" t="s">
+        <v>98</v>
+      </c>
+      <c r="G133" t="s">
         <v>689</v>
       </c>
-      <c r="E133" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" t="s">
-        <v>31</v>
-      </c>
-      <c r="G133" t="s">
+      <c r="H133" t="s">
         <v>690</v>
       </c>
-      <c r="H133" t="s">
+      <c r="I133" t="s">
         <v>691</v>
-      </c>
-      <c r="I133" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>692</v>
+      </c>
+      <c r="B134" t="s">
+        <v>36</v>
+      </c>
+      <c r="C134" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" t="s">
         <v>693</v>
       </c>
-      <c r="B134" t="s">
-        <v>10</v>
-      </c>
-      <c r="C134" t="s">
-        <v>11</v>
-      </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" t="s">
+        <v>98</v>
+      </c>
+      <c r="G134" t="s">
         <v>694</v>
       </c>
-      <c r="E134" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" t="s">
-        <v>14</v>
-      </c>
-      <c r="G134" t="s">
+      <c r="H134" t="s">
         <v>695</v>
-      </c>
-      <c r="H134" t="s">
-        <v>10</v>
       </c>
       <c r="I134" t="s">
         <v>696</v>
@@ -7019,97 +7292,97 @@
         <v>697</v>
       </c>
       <c r="B135" t="s">
-        <v>18</v>
+        <v>698</v>
       </c>
       <c r="C135" t="s">
         <v>10</v>
       </c>
       <c r="D135" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E135" t="s">
         <v>13</v>
       </c>
       <c r="F135" t="s">
-        <v>20</v>
+        <v>700</v>
       </c>
       <c r="G135" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="H135" t="s">
-        <v>461</v>
+        <v>702</v>
       </c>
       <c r="I135" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B136" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C136" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D136" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E136" t="s">
         <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G136" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H136" t="s">
-        <v>10</v>
+        <v>707</v>
       </c>
       <c r="I136" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B137" t="s">
-        <v>706</v>
+        <v>10</v>
       </c>
       <c r="C137" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E137" t="s">
         <v>13</v>
       </c>
       <c r="F137" t="s">
-        <v>708</v>
+        <v>14</v>
       </c>
       <c r="G137" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="H137" t="s">
-        <v>710</v>
+        <v>10</v>
       </c>
       <c r="I137" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B138" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C138" t="s">
-        <v>713</v>
+        <v>10</v>
       </c>
       <c r="D138" t="s">
         <v>714</v>
@@ -7118,13 +7391,13 @@
         <v>13</v>
       </c>
       <c r="F138" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G138" t="s">
         <v>715</v>
       </c>
       <c r="H138" t="s">
-        <v>10</v>
+        <v>461</v>
       </c>
       <c r="I138" t="s">
         <v>716</v>
@@ -7135,48 +7408,48 @@
         <v>717</v>
       </c>
       <c r="B139" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" t="s">
+        <v>14</v>
+      </c>
+      <c r="D139" t="s">
         <v>718</v>
       </c>
-      <c r="C139" t="s">
-        <v>10</v>
-      </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139" t="s">
         <v>719</v>
       </c>
-      <c r="E139" t="s">
-        <v>13</v>
-      </c>
-      <c r="F139" t="s">
-        <v>116</v>
-      </c>
-      <c r="G139" t="s">
+      <c r="H139" t="s">
+        <v>10</v>
+      </c>
+      <c r="I139" t="s">
         <v>720</v>
-      </c>
-      <c r="H139" t="s">
-        <v>721</v>
-      </c>
-      <c r="I139" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>721</v>
+      </c>
+      <c r="B140" t="s">
+        <v>722</v>
+      </c>
+      <c r="C140" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" t="s">
         <v>723</v>
       </c>
-      <c r="B140" t="s">
-        <v>84</v>
-      </c>
-      <c r="C140" t="s">
-        <v>10</v>
-      </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
+        <v>13</v>
+      </c>
+      <c r="F140" t="s">
         <v>724</v>
-      </c>
-      <c r="E140" t="s">
-        <v>13</v>
-      </c>
-      <c r="F140" t="s">
-        <v>31</v>
       </c>
       <c r="G140" t="s">
         <v>725</v>
@@ -7196,10 +7469,10 @@
         <v>10</v>
       </c>
       <c r="C141" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="D141" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E141" t="s">
         <v>13</v>
@@ -7208,56 +7481,56 @@
         <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H141" t="s">
         <v>10</v>
       </c>
       <c r="I141" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B142" t="s">
-        <v>36</v>
+        <v>734</v>
       </c>
       <c r="C142" t="s">
         <v>10</v>
       </c>
       <c r="D142" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E142" t="s">
         <v>13</v>
       </c>
       <c r="F142" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="G142" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="H142" t="s">
-        <v>659</v>
+        <v>737</v>
       </c>
       <c r="I142" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C143" t="s">
         <v>10</v>
       </c>
       <c r="D143" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="E143" t="s">
         <v>13</v>
@@ -7266,56 +7539,56 @@
         <v>31</v>
       </c>
       <c r="G143" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="H143" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="I143" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B144" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C144" t="s">
-        <v>10</v>
+        <v>729</v>
       </c>
       <c r="D144" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E144" t="s">
         <v>13</v>
       </c>
       <c r="F144" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G144" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="H144" t="s">
-        <v>744</v>
+        <v>10</v>
       </c>
       <c r="I144" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B145" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="C145" t="s">
         <v>10</v>
       </c>
       <c r="D145" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E145" t="s">
         <v>13</v>
@@ -7324,56 +7597,56 @@
         <v>31</v>
       </c>
       <c r="G145" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="H145" t="s">
-        <v>749</v>
+        <v>660</v>
       </c>
       <c r="I145" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B146" t="s">
-        <v>718</v>
+        <v>36</v>
       </c>
       <c r="C146" t="s">
         <v>10</v>
       </c>
       <c r="D146" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E146" t="s">
         <v>13</v>
       </c>
       <c r="F146" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="G146" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H146" t="s">
-        <v>721</v>
+        <v>755</v>
       </c>
       <c r="I146" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C147" t="s">
         <v>10</v>
       </c>
       <c r="D147" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E147" t="s">
         <v>13</v>
@@ -7382,18 +7655,18 @@
         <v>31</v>
       </c>
       <c r="G147" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="H147" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="I147" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B148" t="s">
         <v>84</v>
@@ -7402,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="D148" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E148" t="s">
         <v>13</v>
@@ -7411,111 +7684,111 @@
         <v>31</v>
       </c>
       <c r="G148" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="H148" t="s">
-        <v>726</v>
+        <v>765</v>
       </c>
       <c r="I148" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>734</v>
       </c>
       <c r="C149" t="s">
-        <v>713</v>
+        <v>10</v>
       </c>
       <c r="D149" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="E149" t="s">
         <v>13</v>
       </c>
       <c r="F149" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="G149" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="H149" t="s">
-        <v>10</v>
+        <v>737</v>
       </c>
       <c r="I149" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B150" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C150" t="s">
-        <v>713</v>
+        <v>10</v>
       </c>
       <c r="D150" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="E150" t="s">
         <v>13</v>
       </c>
       <c r="F150" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G150" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="H150" t="s">
-        <v>10</v>
+        <v>774</v>
       </c>
       <c r="I150" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B151" t="s">
-        <v>773</v>
+        <v>84</v>
       </c>
       <c r="C151" t="s">
         <v>10</v>
       </c>
       <c r="D151" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E151" t="s">
         <v>13</v>
       </c>
       <c r="F151" t="s">
-        <v>775</v>
+        <v>31</v>
       </c>
       <c r="G151" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="H151" t="s">
-        <v>777</v>
+        <v>742</v>
       </c>
       <c r="I151" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B152" t="s">
-        <v>780</v>
+        <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>10</v>
+        <v>729</v>
       </c>
       <c r="D152" t="s">
         <v>781</v>
@@ -7524,111 +7797,111 @@
         <v>13</v>
       </c>
       <c r="F152" t="s">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="G152" t="s">
         <v>782</v>
       </c>
       <c r="H152" t="s">
+        <v>10</v>
+      </c>
+      <c r="I152" t="s">
         <v>783</v>
-      </c>
-      <c r="I152" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>784</v>
+      </c>
+      <c r="B153" t="s">
+        <v>84</v>
+      </c>
+      <c r="C153" t="s">
+        <v>10</v>
+      </c>
+      <c r="D153" t="s">
         <v>785</v>
       </c>
-      <c r="B153" t="s">
-        <v>780</v>
-      </c>
-      <c r="C153" t="s">
-        <v>10</v>
-      </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" t="s">
+        <v>31</v>
+      </c>
+      <c r="G153" t="s">
         <v>786</v>
       </c>
-      <c r="E153" t="s">
-        <v>13</v>
-      </c>
-      <c r="F153" t="s">
-        <v>116</v>
-      </c>
-      <c r="G153" t="s">
+      <c r="H153" t="s">
         <v>787</v>
       </c>
-      <c r="H153" t="s">
+      <c r="I153" t="s">
         <v>788</v>
-      </c>
-      <c r="I153" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>789</v>
+      </c>
+      <c r="B154" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" t="s">
+        <v>729</v>
+      </c>
+      <c r="D154" t="s">
         <v>790</v>
       </c>
-      <c r="B154" t="s">
+      <c r="E154" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" t="s">
         <v>791</v>
       </c>
-      <c r="C154" t="s">
-        <v>10</v>
-      </c>
-      <c r="D154" t="s">
+      <c r="H154" t="s">
+        <v>10</v>
+      </c>
+      <c r="I154" t="s">
         <v>792</v>
-      </c>
-      <c r="E154" t="s">
-        <v>13</v>
-      </c>
-      <c r="F154" t="s">
-        <v>793</v>
-      </c>
-      <c r="G154" t="s">
-        <v>794</v>
-      </c>
-      <c r="H154" t="s">
-        <v>10</v>
-      </c>
-      <c r="I154" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>793</v>
+      </c>
+      <c r="B155" t="s">
+        <v>794</v>
+      </c>
+      <c r="C155" t="s">
+        <v>10</v>
+      </c>
+      <c r="D155" t="s">
+        <v>795</v>
+      </c>
+      <c r="E155" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" t="s">
         <v>796</v>
       </c>
-      <c r="B155" t="s">
-        <v>36</v>
-      </c>
-      <c r="C155" t="s">
-        <v>10</v>
-      </c>
-      <c r="D155" t="s">
+      <c r="G155" t="s">
         <v>797</v>
       </c>
-      <c r="E155" t="s">
-        <v>13</v>
-      </c>
-      <c r="F155" t="s">
-        <v>31</v>
-      </c>
-      <c r="G155" t="s">
+      <c r="H155" t="s">
         <v>798</v>
       </c>
-      <c r="H155" t="s">
+      <c r="I155" t="s">
         <v>799</v>
-      </c>
-      <c r="I155" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>800</v>
+      </c>
+      <c r="B156" t="s">
         <v>801</v>
-      </c>
-      <c r="B156" t="s">
-        <v>90</v>
       </c>
       <c r="C156" t="s">
         <v>10</v>
@@ -7640,7 +7913,7 @@
         <v>13</v>
       </c>
       <c r="F156" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="G156" t="s">
         <v>803</v>
@@ -7657,7 +7930,7 @@
         <v>806</v>
       </c>
       <c r="B157" t="s">
-        <v>36</v>
+        <v>801</v>
       </c>
       <c r="C157" t="s">
         <v>10</v>
@@ -7669,7 +7942,7 @@
         <v>13</v>
       </c>
       <c r="F157" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="G157" t="s">
         <v>808</v>
@@ -7686,42 +7959,42 @@
         <v>811</v>
       </c>
       <c r="B158" t="s">
-        <v>36</v>
+        <v>812</v>
       </c>
       <c r="C158" t="s">
         <v>10</v>
       </c>
       <c r="D158" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E158" t="s">
         <v>13</v>
       </c>
       <c r="F158" t="s">
-        <v>31</v>
+        <v>814</v>
       </c>
       <c r="G158" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="H158" t="s">
-        <v>814</v>
+        <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B159" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="C159" t="s">
         <v>10</v>
       </c>
       <c r="D159" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E159" t="s">
         <v>13</v>
@@ -7730,21 +8003,21 @@
         <v>31</v>
       </c>
       <c r="G159" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H159" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="I159" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B160" t="s">
-        <v>822</v>
+        <v>90</v>
       </c>
       <c r="C160" t="s">
         <v>10</v>
@@ -7773,7 +8046,7 @@
         <v>827</v>
       </c>
       <c r="B161" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="C161" t="s">
         <v>10</v>
@@ -7802,7 +8075,7 @@
         <v>832</v>
       </c>
       <c r="B162" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="C162" t="s">
         <v>10</v>
@@ -7831,7 +8104,7 @@
         <v>837</v>
       </c>
       <c r="B163" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C163" t="s">
         <v>10</v>
@@ -7860,13 +8133,13 @@
         <v>842</v>
       </c>
       <c r="B164" t="s">
-        <v>36</v>
+        <v>843</v>
       </c>
       <c r="C164" t="s">
         <v>10</v>
       </c>
       <c r="D164" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E164" t="s">
         <v>13</v>
@@ -7875,18 +8148,18 @@
         <v>31</v>
       </c>
       <c r="G164" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H164" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="I164" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B165" t="s">
         <v>84</v>
@@ -7895,7 +8168,7 @@
         <v>10</v>
       </c>
       <c r="D165" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E165" t="s">
         <v>13</v>
@@ -7904,27 +8177,27 @@
         <v>31</v>
       </c>
       <c r="G165" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H165" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="I165" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>84</v>
       </c>
       <c r="C166" t="s">
         <v>10</v>
       </c>
       <c r="D166" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E166" t="s">
         <v>13</v>
@@ -7933,27 +8206,27 @@
         <v>31</v>
       </c>
       <c r="G166" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H166" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I166" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B167" t="s">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="C167" t="s">
         <v>10</v>
       </c>
       <c r="D167" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E167" t="s">
         <v>13</v>
@@ -7962,18 +8235,18 @@
         <v>31</v>
       </c>
       <c r="G167" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H167" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I167" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B168" t="s">
         <v>36</v>
@@ -7982,7 +8255,7 @@
         <v>10</v>
       </c>
       <c r="D168" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E168" t="s">
         <v>13</v>
@@ -7991,18 +8264,18 @@
         <v>31</v>
       </c>
       <c r="G168" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H168" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I168" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B169" t="s">
         <v>84</v>
@@ -8011,7 +8284,7 @@
         <v>10</v>
       </c>
       <c r="D169" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E169" t="s">
         <v>13</v>
@@ -8020,27 +8293,27 @@
         <v>31</v>
       </c>
       <c r="G169" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H169" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="I169" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B170" t="s">
-        <v>36</v>
+        <v>237</v>
       </c>
       <c r="C170" t="s">
         <v>10</v>
       </c>
       <c r="D170" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E170" t="s">
         <v>13</v>
@@ -8049,27 +8322,27 @@
         <v>31</v>
       </c>
       <c r="G170" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H170" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="I170" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B171" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="C171" t="s">
         <v>10</v>
       </c>
       <c r="D171" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E171" t="s">
         <v>13</v>
@@ -8078,21 +8351,21 @@
         <v>31</v>
       </c>
       <c r="G171" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H171" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="I171" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B172" t="s">
-        <v>883</v>
+        <v>36</v>
       </c>
       <c r="C172" t="s">
         <v>10</v>
@@ -8150,57 +8423,579 @@
         <v>893</v>
       </c>
       <c r="B174" t="s">
+        <v>36</v>
+      </c>
+      <c r="C174" t="s">
+        <v>10</v>
+      </c>
+      <c r="D174" t="s">
         <v>894</v>
       </c>
-      <c r="C174" t="s">
-        <v>10</v>
-      </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" t="s">
+        <v>31</v>
+      </c>
+      <c r="G174" t="s">
         <v>895</v>
       </c>
-      <c r="E174" t="s">
-        <v>13</v>
-      </c>
-      <c r="F174" t="s">
-        <v>775</v>
-      </c>
-      <c r="G174" t="s">
+      <c r="H174" t="s">
         <v>896</v>
       </c>
-      <c r="H174" t="s">
+      <c r="I174" t="s">
         <v>897</v>
-      </c>
-      <c r="I174" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>898</v>
+      </c>
+      <c r="B175" t="s">
+        <v>84</v>
+      </c>
+      <c r="C175" t="s">
+        <v>10</v>
+      </c>
+      <c r="D175" t="s">
         <v>899</v>
       </c>
-      <c r="B175" t="s">
+      <c r="E175" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" t="s">
+        <v>31</v>
+      </c>
+      <c r="G175" t="s">
         <v>900</v>
       </c>
-      <c r="C175" t="s">
-        <v>10</v>
-      </c>
-      <c r="D175" t="s">
+      <c r="H175" t="s">
         <v>901</v>
       </c>
-      <c r="E175" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" t="s">
+      <c r="I175" t="s">
         <v>902</v>
       </c>
-      <c r="G175" t="s">
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>903</v>
       </c>
-      <c r="H175" t="s">
+      <c r="B176" t="s">
+        <v>29</v>
+      </c>
+      <c r="C176" t="s">
+        <v>10</v>
+      </c>
+      <c r="D176" t="s">
         <v>904</v>
       </c>
-      <c r="I175" t="s">
+      <c r="E176" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" t="s">
+        <v>31</v>
+      </c>
+      <c r="G176" t="s">
         <v>905</v>
+      </c>
+      <c r="H176" t="s">
+        <v>906</v>
+      </c>
+      <c r="I176" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>908</v>
+      </c>
+      <c r="B177" t="s">
+        <v>36</v>
+      </c>
+      <c r="C177" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177" t="s">
+        <v>909</v>
+      </c>
+      <c r="E177" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" t="s">
+        <v>31</v>
+      </c>
+      <c r="G177" t="s">
+        <v>910</v>
+      </c>
+      <c r="H177" t="s">
+        <v>911</v>
+      </c>
+      <c r="I177" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>913</v>
+      </c>
+      <c r="B178" t="s">
+        <v>36</v>
+      </c>
+      <c r="C178" t="s">
+        <v>10</v>
+      </c>
+      <c r="D178" t="s">
+        <v>914</v>
+      </c>
+      <c r="E178" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" t="s">
+        <v>31</v>
+      </c>
+      <c r="G178" t="s">
+        <v>915</v>
+      </c>
+      <c r="H178" t="s">
+        <v>916</v>
+      </c>
+      <c r="I178" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>918</v>
+      </c>
+      <c r="B179" t="s">
+        <v>36</v>
+      </c>
+      <c r="C179" t="s">
+        <v>10</v>
+      </c>
+      <c r="D179" t="s">
+        <v>919</v>
+      </c>
+      <c r="E179" t="s">
+        <v>13</v>
+      </c>
+      <c r="F179" t="s">
+        <v>31</v>
+      </c>
+      <c r="G179" t="s">
+        <v>920</v>
+      </c>
+      <c r="H179" t="s">
+        <v>921</v>
+      </c>
+      <c r="I179" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>923</v>
+      </c>
+      <c r="B180" t="s">
+        <v>90</v>
+      </c>
+      <c r="C180" t="s">
+        <v>10</v>
+      </c>
+      <c r="D180" t="s">
+        <v>924</v>
+      </c>
+      <c r="E180" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" t="s">
+        <v>31</v>
+      </c>
+      <c r="G180" t="s">
+        <v>925</v>
+      </c>
+      <c r="H180" t="s">
+        <v>926</v>
+      </c>
+      <c r="I180" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>928</v>
+      </c>
+      <c r="B181" t="s">
+        <v>84</v>
+      </c>
+      <c r="C181" t="s">
+        <v>10</v>
+      </c>
+      <c r="D181" t="s">
+        <v>929</v>
+      </c>
+      <c r="E181" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181" t="s">
+        <v>31</v>
+      </c>
+      <c r="G181" t="s">
+        <v>930</v>
+      </c>
+      <c r="H181" t="s">
+        <v>931</v>
+      </c>
+      <c r="I181" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>933</v>
+      </c>
+      <c r="B182" t="s">
+        <v>934</v>
+      </c>
+      <c r="C182" t="s">
+        <v>10</v>
+      </c>
+      <c r="D182" t="s">
+        <v>935</v>
+      </c>
+      <c r="E182" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" t="s">
+        <v>31</v>
+      </c>
+      <c r="G182" t="s">
+        <v>936</v>
+      </c>
+      <c r="H182" t="s">
+        <v>937</v>
+      </c>
+      <c r="I182" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>939</v>
+      </c>
+      <c r="B183" t="s">
+        <v>84</v>
+      </c>
+      <c r="C183" t="s">
+        <v>10</v>
+      </c>
+      <c r="D183" t="s">
+        <v>940</v>
+      </c>
+      <c r="E183" t="s">
+        <v>13</v>
+      </c>
+      <c r="F183" t="s">
+        <v>31</v>
+      </c>
+      <c r="G183" t="s">
+        <v>941</v>
+      </c>
+      <c r="H183" t="s">
+        <v>942</v>
+      </c>
+      <c r="I183" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>944</v>
+      </c>
+      <c r="B184" t="s">
+        <v>36</v>
+      </c>
+      <c r="C184" t="s">
+        <v>10</v>
+      </c>
+      <c r="D184" t="s">
+        <v>945</v>
+      </c>
+      <c r="E184" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" t="s">
+        <v>31</v>
+      </c>
+      <c r="G184" t="s">
+        <v>946</v>
+      </c>
+      <c r="H184" t="s">
+        <v>947</v>
+      </c>
+      <c r="I184" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>949</v>
+      </c>
+      <c r="B185" t="s">
+        <v>934</v>
+      </c>
+      <c r="C185" t="s">
+        <v>10</v>
+      </c>
+      <c r="D185" t="s">
+        <v>950</v>
+      </c>
+      <c r="E185" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" t="s">
+        <v>31</v>
+      </c>
+      <c r="G185" t="s">
+        <v>951</v>
+      </c>
+      <c r="H185" t="s">
+        <v>952</v>
+      </c>
+      <c r="I185" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>954</v>
+      </c>
+      <c r="B186" t="s">
+        <v>195</v>
+      </c>
+      <c r="C186" t="s">
+        <v>10</v>
+      </c>
+      <c r="D186" t="s">
+        <v>955</v>
+      </c>
+      <c r="E186" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" t="s">
+        <v>31</v>
+      </c>
+      <c r="G186" t="s">
+        <v>956</v>
+      </c>
+      <c r="H186" t="s">
+        <v>957</v>
+      </c>
+      <c r="I186" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>959</v>
+      </c>
+      <c r="B187" t="s">
+        <v>29</v>
+      </c>
+      <c r="C187" t="s">
+        <v>10</v>
+      </c>
+      <c r="D187" t="s">
+        <v>960</v>
+      </c>
+      <c r="E187" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" t="s">
+        <v>31</v>
+      </c>
+      <c r="G187" t="s">
+        <v>961</v>
+      </c>
+      <c r="H187" t="s">
+        <v>962</v>
+      </c>
+      <c r="I187" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>964</v>
+      </c>
+      <c r="B188" t="s">
+        <v>36</v>
+      </c>
+      <c r="C188" t="s">
+        <v>10</v>
+      </c>
+      <c r="D188" t="s">
+        <v>965</v>
+      </c>
+      <c r="E188" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188" t="s">
+        <v>31</v>
+      </c>
+      <c r="G188" t="s">
+        <v>966</v>
+      </c>
+      <c r="H188" t="s">
+        <v>967</v>
+      </c>
+      <c r="I188" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>969</v>
+      </c>
+      <c r="B189" t="s">
+        <v>36</v>
+      </c>
+      <c r="C189" t="s">
+        <v>10</v>
+      </c>
+      <c r="D189" t="s">
+        <v>970</v>
+      </c>
+      <c r="E189" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" t="s">
+        <v>31</v>
+      </c>
+      <c r="G189" t="s">
+        <v>971</v>
+      </c>
+      <c r="H189" t="s">
+        <v>972</v>
+      </c>
+      <c r="I189" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>974</v>
+      </c>
+      <c r="B190" t="s">
+        <v>36</v>
+      </c>
+      <c r="C190" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190" t="s">
+        <v>975</v>
+      </c>
+      <c r="E190" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" t="s">
+        <v>31</v>
+      </c>
+      <c r="G190" t="s">
+        <v>976</v>
+      </c>
+      <c r="H190" t="s">
+        <v>977</v>
+      </c>
+      <c r="I190" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>979</v>
+      </c>
+      <c r="B191" t="s">
+        <v>36</v>
+      </c>
+      <c r="C191" t="s">
+        <v>10</v>
+      </c>
+      <c r="D191" t="s">
+        <v>980</v>
+      </c>
+      <c r="E191" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" t="s">
+        <v>31</v>
+      </c>
+      <c r="G191" t="s">
+        <v>981</v>
+      </c>
+      <c r="H191" t="s">
+        <v>982</v>
+      </c>
+      <c r="I191" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>984</v>
+      </c>
+      <c r="B192" t="s">
+        <v>985</v>
+      </c>
+      <c r="C192" t="s">
+        <v>10</v>
+      </c>
+      <c r="D192" t="s">
+        <v>986</v>
+      </c>
+      <c r="E192" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" t="s">
+        <v>796</v>
+      </c>
+      <c r="G192" t="s">
+        <v>987</v>
+      </c>
+      <c r="H192" t="s">
+        <v>988</v>
+      </c>
+      <c r="I192" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>990</v>
+      </c>
+      <c r="B193" t="s">
+        <v>991</v>
+      </c>
+      <c r="C193" t="s">
+        <v>10</v>
+      </c>
+      <c r="D193" t="s">
+        <v>992</v>
+      </c>
+      <c r="E193" t="s">
+        <v>13</v>
+      </c>
+      <c r="F193" t="s">
+        <v>993</v>
+      </c>
+      <c r="G193" t="s">
+        <v>994</v>
+      </c>
+      <c r="H193" t="s">
+        <v>995</v>
+      </c>
+      <c r="I193" t="s">
+        <v>996</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-app-entry.report.xlsx
+++ b/tools/importer/reports/import-app-entry.report.xlsx
@@ -1030,7 +1030,7 @@
     <t>app-entry</t>
   </si>
   <si>
-    <t>2026-10-24T00:55:47.134Z</t>
+    <t>2026-10-24T08:28:12.608Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/at/de/flugsuche</t>
@@ -1162,7 +1162,7 @@
     <t>at/de/gepaeck</t>
   </si>
   <si>
-    <t>2026-10-24T00:57:44.935Z</t>
+    <t>2026-10-24T08:19:23.748Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/at/de/gepaeck</t>
@@ -1735,7 +1735,7 @@
     <t>at/de/miles-and-more</t>
   </si>
   <si>
-    <t>2026-10-24T00:57:52.050Z</t>
+    <t>2026-10-24T08:19:25.609Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/at/de/miles-and-more</t>
@@ -3448,7 +3448,7 @@
     <t>de/de/flugsuche</t>
   </si>
   <si>
-    <t>2026-10-24T00:55:57.428Z</t>
+    <t>2026-10-24T08:28:14.965Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/de/flugsuche</t>
@@ -3559,7 +3559,7 @@
     <t>de/de/gepaeck</t>
   </si>
   <si>
-    <t>2026-10-24T00:58:07.054Z</t>
+    <t>2026-10-24T08:19:28.205Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/de/gepaeck</t>
@@ -4075,7 +4075,7 @@
     <t>de/de/miles-and-more</t>
   </si>
   <si>
-    <t>2026-10-24T00:58:13.904Z</t>
+    <t>2026-10-24T08:19:30.412Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/de/miles-and-more</t>
@@ -5161,7 +5161,7 @@
     <t>de/en/baggage</t>
   </si>
   <si>
-    <t>2026-10-24T00:58:30.914Z</t>
+    <t>2026-10-24T08:19:33.950Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/baggage</t>
@@ -5761,7 +5761,7 @@
     <t>de/en/flight-search</t>
   </si>
   <si>
-    <t>2026-10-24T00:56:05.999Z</t>
+    <t>2026-10-24T08:28:17.338Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/flight-search</t>
@@ -6322,7 +6322,7 @@
     <t>de/en/miles-and-more</t>
   </si>
   <si>
-    <t>2026-10-24T00:58:43.146Z</t>
+    <t>2026-10-24T08:19:36.025Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/de/en/miles-and-more</t>
@@ -7432,7 +7432,7 @@
     <t>gb/en/baggage</t>
   </si>
   <si>
-    <t>2026-10-24T00:58:54.876Z</t>
+    <t>2026-10-24T08:19:38.430Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/gb/en/baggage</t>
@@ -8032,7 +8032,7 @@
     <t>gb/en/flight-search</t>
   </si>
   <si>
-    <t>2026-10-24T00:56:16.733Z</t>
+    <t>2026-10-24T08:28:20.153Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/gb/en/flight-search</t>
@@ -8176,7 +8176,7 @@
     <t>gb/en/general-conditions-currency-conversion</t>
   </si>
   <si>
-    <t>2026-10-23T05:23:15.158Z</t>
+    <t>2026-10-24T08:19:53.283Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/gb/en/general-conditions-currency-conversion</t>
@@ -8584,7 +8584,7 @@
     <t>gb/en/miles-and-more</t>
   </si>
   <si>
-    <t>2026-10-24T00:59:06.791Z</t>
+    <t>2026-10-24T08:19:40.985Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/gb/en/miles-and-more</t>
@@ -8968,7 +8968,7 @@
     <t>gb/en/sepa-terms-and-conditions-b</t>
   </si>
   <si>
-    <t>2026-10-23T05:24:09.032Z</t>
+    <t>2026-10-24T08:19:55.410Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/gb/en/sepa-terms-and-conditions-b</t>
@@ -9100,7 +9100,7 @@
     <t>gb/en/terms-and-conditions-lh</t>
   </si>
   <si>
-    <t>2026-10-23T05:24:20.354Z</t>
+    <t>2026-10-24T08:19:58.361Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/gb/en/terms-and-conditions-lh</t>
@@ -10837,7 +10837,7 @@
     <t>gb/en/common/accessibility-statement</t>
   </si>
   <si>
-    <t>2026-10-23T05:13:55.116Z</t>
+    <t>2026-10-24T08:19:51.399Z</t>
   </si>
   <si>
     <t>https://www.lufthansa.com/gb/en/common/accessibility-statement</t>
